--- a/Audit_Buffer_120.xlsx
+++ b/Audit_Buffer_120.xlsx
@@ -453,34 +453,34 @@
         <v>46158</v>
       </c>
       <c r="C2" t="str">
-        <v>LAFALI KONE</v>
+        <v>Guy-Evrard Fodjo</v>
       </c>
       <c r="D2" t="str">
-        <v>ABVI.02.03</v>
+        <v>ABVD.02.04</v>
       </c>
       <c r="E2" t="str">
-        <v>Twins Bar</v>
+        <v>TAXIS GARE VIP</v>
       </c>
       <c r="F2">
-        <v>10449991</v>
+        <v>10442849</v>
       </c>
       <c r="G2" t="str">
-        <v>DB010126N024105</v>
+        <v>DB010126N002566</v>
       </c>
       <c r="H2" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I2" t="str">
-        <v>Bar Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J2">
-        <v>574037587</v>
+        <v>554200930</v>
       </c>
       <c r="K2">
-        <v>5.266051</v>
+        <v>5.44405</v>
       </c>
       <c r="L2">
-        <v>-3.9869411</v>
+        <v>-4.05303</v>
       </c>
     </row>
     <row r="3">
@@ -491,34 +491,34 @@
         <v>46158</v>
       </c>
       <c r="C3" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>MARC AMON</v>
       </c>
       <c r="D3" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVD.01.07</v>
       </c>
       <c r="E3" t="str">
-        <v>Restaurant KELKEPART BY JOËL</v>
+        <v>Au piment</v>
       </c>
       <c r="F3">
-        <v>10449745</v>
+        <v>10445283</v>
       </c>
       <c r="G3" t="str">
-        <v>DB010126N023418</v>
+        <v>DB010126N004328</v>
       </c>
       <c r="H3" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I3" t="str">
-        <v>RESTAURANT PREMIUM</v>
+        <v>Maquis</v>
       </c>
       <c r="J3">
-        <v>151702177</v>
+        <v>153332530</v>
       </c>
       <c r="K3">
-        <v>5.3411583</v>
+        <v>5.31167</v>
       </c>
       <c r="L3">
-        <v>-4.0029807</v>
+        <v>-4.0753</v>
       </c>
     </row>
     <row r="4">
@@ -529,34 +529,34 @@
         <v>46158</v>
       </c>
       <c r="C4" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>ALEXANDRE TIEGBE</v>
       </c>
       <c r="D4" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVI.01.02</v>
       </c>
       <c r="E4" t="str">
-        <v>Le king</v>
+        <v>La côte d'azur</v>
       </c>
       <c r="F4">
-        <v>10449727</v>
+        <v>10432936</v>
       </c>
       <c r="G4" t="str">
-        <v>DB010126N018158</v>
+        <v>DB010126N014932</v>
       </c>
       <c r="H4" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I4" t="str">
-        <v>MAQUIS RESTAURANT</v>
-      </c>
-      <c r="J4">
-        <v>101350721</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J4" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K4">
-        <v>5.3279727</v>
+        <v>5.40097</v>
       </c>
       <c r="L4">
-        <v>-3.9227523</v>
+        <v>-4.00666</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         <v>46158</v>
       </c>
       <c r="C5" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>HERMANN GOGOUA</v>
       </c>
       <c r="D5" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVI.04.02</v>
       </c>
       <c r="E5" t="str">
-        <v>Le pouvoir</v>
+        <v>Ferme monatin</v>
       </c>
       <c r="F5">
-        <v>10434607</v>
+        <v>10436629</v>
       </c>
       <c r="G5" t="str">
-        <v>DB010126N000684</v>
+        <v>DB010126N001385</v>
       </c>
       <c r="H5" t="str">
         <v>ABIDJAN</v>
@@ -591,10 +591,10 @@
         <v>(blank)</v>
       </c>
       <c r="K5">
-        <v>5.37496</v>
+        <v>5.3275</v>
       </c>
       <c r="L5">
-        <v>-4.00481</v>
+        <v>-4.00098</v>
       </c>
     </row>
     <row r="6">
@@ -605,19 +605,19 @@
         <v>46158</v>
       </c>
       <c r="C6" t="str">
-        <v>FRANCK KOUADIO</v>
+        <v>VERCRUSSE AGAH</v>
       </c>
       <c r="D6" t="str">
-        <v>ABVD.02.03</v>
+        <v>ABVI.05.02</v>
       </c>
       <c r="E6" t="str">
-        <v>La cave au quartier</v>
+        <v>O’BAMBOU CHEZ LE RICHE</v>
       </c>
       <c r="F6">
-        <v>10435230</v>
+        <v>10448761</v>
       </c>
       <c r="G6" t="str">
-        <v>DB010126N000887</v>
+        <v>DB010126N006152</v>
       </c>
       <c r="H6" t="str">
         <v>ABIDJAN</v>
@@ -629,10 +629,10 @@
         <v>(blank)</v>
       </c>
       <c r="K6">
-        <v>5.34145</v>
+        <v>5.4605</v>
       </c>
       <c r="L6">
-        <v>-4.11531</v>
+        <v>-4.04279</v>
       </c>
     </row>
     <row r="7">
@@ -643,34 +643,34 @@
         <v>46158</v>
       </c>
       <c r="C7" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>Innocent Yoboue</v>
       </c>
       <c r="D7" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVI.02.05</v>
       </c>
       <c r="E7" t="str">
-        <v xml:space="preserve">5 ÉTOILES </v>
+        <v>Cave du port</v>
       </c>
       <c r="F7">
-        <v>10448867</v>
+        <v>10449927</v>
       </c>
       <c r="G7" t="str">
-        <v>DB270226N006217</v>
+        <v>DB010126N006511</v>
       </c>
       <c r="H7" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I7" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J7">
-        <v>153721478</v>
+        <v>707332348</v>
       </c>
       <c r="K7">
-        <v>5.30884</v>
+        <v>5.30326</v>
       </c>
       <c r="L7">
-        <v>-4.03789</v>
+        <v>-3.96435</v>
       </c>
     </row>
     <row r="8">
@@ -681,34 +681,34 @@
         <v>46158</v>
       </c>
       <c r="C8" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>JOSEPH ABOUA</v>
       </c>
       <c r="D8" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVI.03.03</v>
       </c>
       <c r="E8" t="str">
-        <v>Chez Florence</v>
+        <v>Évidence</v>
       </c>
       <c r="F8">
-        <v>10434532</v>
+        <v>10436454</v>
       </c>
       <c r="G8" t="str">
-        <v>DB010126N000649</v>
+        <v>DB010126N001325</v>
       </c>
       <c r="H8" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I8" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis Choco</v>
       </c>
       <c r="J8" t="str">
         <v>(blank)</v>
       </c>
       <c r="K8">
-        <v>5.37669</v>
+        <v>5.24114</v>
       </c>
       <c r="L8">
-        <v>-3.97371</v>
+        <v>-3.88358</v>
       </c>
     </row>
     <row r="9">
@@ -719,19 +719,19 @@
         <v>46158</v>
       </c>
       <c r="C9" t="str">
-        <v>FRANCK YAO</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D9" t="str">
-        <v>ABVI.03.02</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E9" t="str">
-        <v>Maquis Zinzin</v>
+        <v>Chez AAl</v>
       </c>
       <c r="F9">
-        <v>10450607</v>
+        <v>10439389</v>
       </c>
       <c r="G9" t="str">
-        <v>DB010126N022095</v>
+        <v>DB010126N002296</v>
       </c>
       <c r="H9" t="str">
         <v>ABIDJAN</v>
@@ -739,14 +739,14 @@
       <c r="I9" t="str">
         <v>Maquis Standard</v>
       </c>
-      <c r="J9">
-        <v>748406014</v>
+      <c r="J9" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K9">
-        <v>5.24843</v>
+        <v>5.36126</v>
       </c>
       <c r="L9">
-        <v>-3.9487083</v>
+        <v>-3.96967</v>
       </c>
     </row>
     <row r="10">
@@ -757,34 +757,34 @@
         <v>46158</v>
       </c>
       <c r="C10" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>MARC AMON</v>
       </c>
       <c r="D10" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVD.01.07</v>
       </c>
       <c r="E10" t="str">
-        <v>Chez Christie</v>
+        <v>Chez caro</v>
       </c>
       <c r="F10">
-        <v>10435834</v>
+        <v>10445422</v>
       </c>
       <c r="G10" t="str">
-        <v>DB010126N001144</v>
+        <v>DB010126N004468</v>
       </c>
       <c r="H10" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I10" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J10">
-        <v>111717177</v>
+        <v>778762538</v>
       </c>
       <c r="K10">
-        <v>5.30434</v>
+        <v>5.31131</v>
       </c>
       <c r="L10">
-        <v>-4.01182</v>
+        <v>-4.08827</v>
       </c>
     </row>
     <row r="11">
@@ -795,34 +795,34 @@
         <v>46158</v>
       </c>
       <c r="C11" t="str">
-        <v>EPONOH ETTIEN</v>
+        <v>Innocent Yoboue</v>
       </c>
       <c r="D11" t="str">
-        <v>ABVI.05.H4</v>
+        <v>ABVI.02.05</v>
       </c>
       <c r="E11" t="str">
-        <v>Espace chez key’T</v>
+        <v>Cave le debout</v>
       </c>
       <c r="F11">
-        <v>10443536</v>
+        <v>10443986</v>
       </c>
       <c r="G11" t="str">
-        <v>DB010126N003252</v>
+        <v>DB010126N003697</v>
       </c>
       <c r="H11" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I11" t="str">
-        <v>Maquis</v>
+        <v>Cave</v>
       </c>
       <c r="J11">
-        <v>777982678</v>
+        <v>777358223</v>
       </c>
       <c r="K11">
-        <v>5.34124</v>
+        <v>5.29839</v>
       </c>
       <c r="L11">
-        <v>-4.1007</v>
+        <v>-3.95078</v>
       </c>
     </row>
     <row r="12">
@@ -839,28 +839,28 @@
         <v>ABVI.04.04</v>
       </c>
       <c r="E12" t="str">
-        <v>MAQUIS ANOUMAMBO</v>
+        <v>Opera plus</v>
       </c>
       <c r="F12">
-        <v>10442996</v>
+        <v>10439953</v>
       </c>
       <c r="G12" t="str">
-        <v>DB010126N002708</v>
+        <v>DB010126N002467</v>
       </c>
       <c r="H12" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I12" t="str">
-        <v>Maquis</v>
+        <v>Bar Standard</v>
       </c>
       <c r="J12" t="str">
-        <v>05 05 26 12 75</v>
+        <v>(blank)</v>
       </c>
       <c r="K12">
-        <v>5.29651</v>
+        <v>5.30486</v>
       </c>
       <c r="L12">
-        <v>-3.74875</v>
+        <v>-3.82276</v>
       </c>
     </row>
     <row r="13">
@@ -871,34 +871,34 @@
         <v>46158</v>
       </c>
       <c r="C13" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>Berenger-Orphée Jenifer Okou</v>
       </c>
       <c r="D13" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVI.02.H2</v>
       </c>
       <c r="E13" t="str">
-        <v>PALMIER ROYAL</v>
+        <v>CHEZ PEKO</v>
       </c>
       <c r="F13">
-        <v>10448881</v>
+        <v>10448298</v>
       </c>
       <c r="G13" t="str">
-        <v>DB270226N006233</v>
+        <v>DB010126N005813</v>
       </c>
       <c r="H13" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I13" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J13">
-        <v>748808029</v>
+        <v>708261910</v>
       </c>
       <c r="K13">
-        <v>5.30883</v>
+        <v>5.3012</v>
       </c>
       <c r="L13">
-        <v>-4.03781</v>
+        <v>-3.99759</v>
       </c>
     </row>
     <row r="14">
@@ -909,34 +909,34 @@
         <v>46160</v>
       </c>
       <c r="C14" t="str">
-        <v>AMINE COULIBALY</v>
+        <v>Berenger-Orphée Jenifer Okou</v>
       </c>
       <c r="D14" t="str">
-        <v>ABVD.01.01</v>
+        <v>ABVI.02.H2</v>
       </c>
       <c r="E14" t="str">
-        <v>CHEZ NICOLE</v>
+        <v>Chez Olivia</v>
       </c>
       <c r="F14">
-        <v>10433082</v>
+        <v>10448319</v>
       </c>
       <c r="G14" t="str">
-        <v>DB010126N000101</v>
+        <v>DB010126N005834</v>
       </c>
       <c r="H14" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I14" t="str">
-        <v>Maquis Choco</v>
-      </c>
-      <c r="J14" t="str">
-        <v>(blank)</v>
+        <v>Maquis</v>
+      </c>
+      <c r="J14">
+        <v>708977729</v>
       </c>
       <c r="K14">
-        <v>5.36782</v>
+        <v>5.30763</v>
       </c>
       <c r="L14">
-        <v>-4.02421</v>
+        <v>-3.98714</v>
       </c>
     </row>
     <row r="15">
@@ -947,19 +947,19 @@
         <v>46160</v>
       </c>
       <c r="C15" t="str">
-        <v>EPONOH ETTIEN</v>
+        <v>JOSEPH ABOUA</v>
       </c>
       <c r="D15" t="str">
-        <v>ABVI.05.H4</v>
+        <v>ABVI.03.03</v>
       </c>
       <c r="E15" t="str">
-        <v>Épopée</v>
+        <v>Cave des roi</v>
       </c>
       <c r="F15">
-        <v>10444239</v>
+        <v>10443395</v>
       </c>
       <c r="G15" t="str">
-        <v>DB010126N003952</v>
+        <v>DB010126N003113</v>
       </c>
       <c r="H15" t="str">
         <v>ABIDJAN</v>
@@ -968,13 +968,13 @@
         <v>Maquis</v>
       </c>
       <c r="J15">
-        <v>707177806</v>
+        <v>758487420</v>
       </c>
       <c r="K15">
-        <v>5.35289</v>
+        <v>5.23902</v>
       </c>
       <c r="L15">
-        <v>-4.09941</v>
+        <v>-3.88956</v>
       </c>
     </row>
     <row r="16">
@@ -985,34 +985,34 @@
         <v>46160</v>
       </c>
       <c r="C16" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D16" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E16" t="str">
-        <v>Chez Willy</v>
+        <v>Gôzô</v>
       </c>
       <c r="F16">
-        <v>10434555</v>
+        <v>10437246</v>
       </c>
       <c r="G16" t="str">
-        <v>DB010126N000660</v>
+        <v>DB010126N001698</v>
       </c>
       <c r="H16" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I16" t="str">
-        <v>Maquis Choco</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J16" t="str">
         <v>(blank)</v>
       </c>
       <c r="K16">
-        <v>5.3753</v>
+        <v>5.28412</v>
       </c>
       <c r="L16">
-        <v>-3.99273</v>
+        <v>-3.96832</v>
       </c>
     </row>
     <row r="17">
@@ -1023,34 +1023,34 @@
         <v>46160</v>
       </c>
       <c r="C17" t="str">
-        <v>FRANCK KOUADIO</v>
+        <v>Innocent Yoboue</v>
       </c>
       <c r="D17" t="str">
-        <v>ABVD.02.03</v>
+        <v>ABVI.02.05</v>
       </c>
       <c r="E17" t="str">
-        <v>Chez Cynthia</v>
+        <v>No PROBLEM 2</v>
       </c>
       <c r="F17">
-        <v>10443446</v>
+        <v>10444997</v>
       </c>
       <c r="G17" t="str">
-        <v>DB010126N003164</v>
+        <v>DB010126N004182</v>
       </c>
       <c r="H17" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I17" t="str">
-        <v>Maquis</v>
+        <v>Cave</v>
       </c>
       <c r="J17">
-        <v>703192941</v>
+        <v>779612662</v>
       </c>
       <c r="K17">
-        <v>5.324579</v>
+        <v>5.30605</v>
       </c>
       <c r="L17">
-        <v>-4.25551</v>
+        <v>-3.94701</v>
       </c>
     </row>
     <row r="18">
@@ -1061,34 +1061,34 @@
         <v>46160</v>
       </c>
       <c r="C18" t="str">
-        <v>JOSEPH ABOUA</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D18" t="str">
-        <v>ABVI.03.03</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E18" t="str">
-        <v>Plein Air du terminus 09</v>
+        <v>Michma services</v>
       </c>
       <c r="F18">
-        <v>10443423</v>
+        <v>10439525</v>
       </c>
       <c r="G18" t="str">
-        <v>DB010126N003141</v>
+        <v>DB010126N002344</v>
       </c>
       <c r="H18" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I18" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J18">
-        <v>102817577</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J18" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K18">
-        <v>5.24471</v>
+        <v>5.34234</v>
       </c>
       <c r="L18">
-        <v>-3.89217</v>
+        <v>-3.96993</v>
       </c>
     </row>
     <row r="19">
@@ -1099,34 +1099,34 @@
         <v>46160</v>
       </c>
       <c r="C19" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>ANGELIQUE KOUASSI</v>
       </c>
       <c r="D19" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVD.02.07</v>
       </c>
       <c r="E19" t="str">
-        <v>Cave chez fatim</v>
+        <v>Maquis aklomybla</v>
       </c>
       <c r="F19">
-        <v>10438201</v>
+        <v>10433377</v>
       </c>
       <c r="G19" t="str">
-        <v>DB010126N001960</v>
+        <v>DB010126N000213</v>
       </c>
       <c r="H19" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I19" t="str">
-        <v>Cave</v>
-      </c>
-      <c r="J19">
-        <v>757821443</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J19" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K19">
-        <v>5.32893</v>
+        <v>5.356</v>
       </c>
       <c r="L19">
-        <v>-4.057015</v>
+        <v>-4.07148</v>
       </c>
     </row>
     <row r="20">
@@ -1137,19 +1137,19 @@
         <v>46160</v>
       </c>
       <c r="C20" t="str">
-        <v>TCHESSE GOHOURE</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D20" t="str">
-        <v>ABVI.02.02</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E20" t="str">
-        <v>Chez Amich</v>
+        <v>AMICI D’ITALIA</v>
       </c>
       <c r="F20">
-        <v>10443127</v>
+        <v>10442993</v>
       </c>
       <c r="G20" t="str">
-        <v>DB010126N002840</v>
+        <v>DB010126N002705</v>
       </c>
       <c r="H20" t="str">
         <v>ABIDJAN</v>
@@ -1158,13 +1158,13 @@
         <v>Maquis</v>
       </c>
       <c r="J20" t="str">
-        <v>0142848821/0797769898</v>
+        <v>05 56 94 91 35</v>
       </c>
       <c r="K20">
-        <v>5.33796</v>
+        <v>5.32805</v>
       </c>
       <c r="L20">
-        <v>-3.97265</v>
+        <v>-3.92076</v>
       </c>
     </row>
     <row r="21">
@@ -1175,34 +1175,34 @@
         <v>46160</v>
       </c>
       <c r="C21" t="str">
-        <v>MARC AMON</v>
+        <v>Berenger-Orphée Jenifer Okou</v>
       </c>
       <c r="D21" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.02.H2</v>
       </c>
       <c r="E21" t="str">
-        <v>O'jardin</v>
+        <v>Le Vallon</v>
       </c>
       <c r="F21">
-        <v>10444225</v>
+        <v>10448373</v>
       </c>
       <c r="G21" t="str">
-        <v>DB010126N003937</v>
+        <v>DB010126N005868</v>
       </c>
       <c r="H21" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I21" t="str">
-        <v>Maquis</v>
+        <v>Cave</v>
       </c>
       <c r="J21">
-        <v>777140929</v>
+        <v>707693519</v>
       </c>
       <c r="K21">
-        <v>5.31545</v>
+        <v>5.30737</v>
       </c>
       <c r="L21">
-        <v>-4.08931</v>
+        <v>-3.98197</v>
       </c>
     </row>
     <row r="22">
@@ -1213,34 +1213,34 @@
         <v>46160</v>
       </c>
       <c r="C22" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>RODRIGUE YOHORE</v>
       </c>
       <c r="D22" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVI.05.04</v>
       </c>
       <c r="E22" t="str">
-        <v>Chez Tantie Alice</v>
+        <v>Espace charmant</v>
       </c>
       <c r="F22">
-        <v>10448313</v>
+        <v>10438933</v>
       </c>
       <c r="G22" t="str">
-        <v>DB010126N005828</v>
+        <v>DB010126N002188</v>
       </c>
       <c r="H22" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I22" t="str">
-        <v>Restaurant</v>
-      </c>
-      <c r="J22">
-        <v>707966758</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J22" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K22">
-        <v>5.3063</v>
+        <v>5.42848</v>
       </c>
       <c r="L22">
-        <v>-3.98178</v>
+        <v>-3.9896</v>
       </c>
     </row>
     <row r="23">
@@ -1251,34 +1251,34 @@
         <v>46160</v>
       </c>
       <c r="C23" t="str">
-        <v>Guy-Evrard Fodjo</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D23" t="str">
-        <v>ABVD.02.04</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E23" t="str">
-        <v>Chez Leï</v>
+        <v>Cave la paix</v>
       </c>
       <c r="F23">
-        <v>10449144</v>
+        <v>10443773</v>
       </c>
       <c r="G23" t="str">
-        <v>DB010126N014511</v>
+        <v>DB010126N003488</v>
       </c>
       <c r="H23" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I23" t="str">
-        <v>Maquis Standard</v>
+        <v>Cave</v>
       </c>
       <c r="J23">
-        <v>708767385</v>
+        <v>103198924</v>
       </c>
       <c r="K23">
-        <v>5.4358667</v>
+        <v>5.33796</v>
       </c>
       <c r="L23">
-        <v>-4.0279133</v>
+        <v>-3.97155</v>
       </c>
     </row>
     <row r="24">
@@ -1289,34 +1289,34 @@
         <v>46160</v>
       </c>
       <c r="C24" t="str">
-        <v>LAFALI KONE</v>
+        <v>FRANCK YAO</v>
       </c>
       <c r="D24" t="str">
-        <v>ABVI.02.03</v>
+        <v>ABVI.03.02</v>
       </c>
       <c r="E24" t="str">
-        <v>Maquis chez tonio</v>
+        <v>Au Kohi</v>
       </c>
       <c r="F24">
-        <v>10437310</v>
+        <v>10443404</v>
       </c>
       <c r="G24" t="str">
-        <v>DB010126N001731</v>
+        <v>DB010126N003122</v>
       </c>
       <c r="H24" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I24" t="str">
-        <v>Maquis Choco</v>
-      </c>
-      <c r="J24" t="str">
-        <v>(blank)</v>
+        <v>Maquis</v>
+      </c>
+      <c r="J24">
+        <v>101260606</v>
       </c>
       <c r="K24">
-        <v>5.28496</v>
+        <v>5.25447</v>
       </c>
       <c r="L24">
-        <v>-3.9613</v>
+        <v>-3.91429</v>
       </c>
     </row>
     <row r="25">
@@ -1327,34 +1327,34 @@
         <v>46160</v>
       </c>
       <c r="C25" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D25" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E25" t="str">
-        <v>Chez Messie</v>
+        <v>Maquis chez tonio</v>
       </c>
       <c r="F25">
-        <v>10448366</v>
+        <v>10437310</v>
       </c>
       <c r="G25" t="str">
-        <v>DB010126N005861</v>
+        <v>DB010126N001731</v>
       </c>
       <c r="H25" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I25" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J25">
-        <v>707806289</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J25" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K25">
-        <v>5.30319</v>
+        <v>5.28496</v>
       </c>
       <c r="L25">
-        <v>-3.99126</v>
+        <v>-3.9613</v>
       </c>
     </row>
     <row r="26">
@@ -1365,34 +1365,34 @@
         <v>46161</v>
       </c>
       <c r="C26" t="str">
-        <v>LANDRY TIEHI</v>
+        <v>MARC AMON</v>
       </c>
       <c r="D26" t="str">
-        <v>ABVD.01.06</v>
+        <v>ABVD.01.07</v>
       </c>
       <c r="E26" t="str">
-        <v>Aquarium</v>
+        <v>Maquis maison mère</v>
       </c>
       <c r="F26">
-        <v>10444918</v>
+        <v>10437792</v>
       </c>
       <c r="G26" t="str">
-        <v>DB010126N004105</v>
+        <v>DB010126N001857</v>
       </c>
       <c r="H26" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I26" t="str">
-        <v>Cave</v>
-      </c>
-      <c r="J26">
-        <v>707250521</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J26" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K26">
-        <v>5.39545</v>
+        <v>5.31695</v>
       </c>
       <c r="L26">
-        <v>-3.98691</v>
+        <v>-4.08492</v>
       </c>
     </row>
     <row r="27">
@@ -1403,19 +1403,19 @@
         <v>46161</v>
       </c>
       <c r="C27" t="str">
-        <v>AIME KONAN</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D27" t="str">
-        <v>ABVI.04.04</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E27" t="str">
-        <v>ESP1CE FAMILLE RESTO LOUNGE</v>
+        <v>Maquis Espace 1000 couleurs</v>
       </c>
       <c r="F27">
-        <v>10443732</v>
+        <v>10443606</v>
       </c>
       <c r="G27" t="str">
-        <v>DB010126N003449</v>
+        <v>DB010126N003322</v>
       </c>
       <c r="H27" t="str">
         <v>ABIDJAN</v>
@@ -1423,14 +1423,14 @@
       <c r="I27" t="str">
         <v>Maquis</v>
       </c>
-      <c r="J27" t="str">
-        <v>07 47 44 31 13</v>
+      <c r="J27">
+        <v>758768764</v>
       </c>
       <c r="K27">
-        <v>5.35972</v>
+        <v>5.34389</v>
       </c>
       <c r="L27">
-        <v>-3.90652</v>
+        <v>-3.97172</v>
       </c>
     </row>
     <row r="28">
@@ -1441,34 +1441,34 @@
         <v>46161</v>
       </c>
       <c r="C28" t="str">
-        <v>MARC AMON</v>
+        <v>JOSEPH ABOUA</v>
       </c>
       <c r="D28" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.03.03</v>
       </c>
       <c r="E28" t="str">
-        <v>Maquis chez Thierry</v>
+        <v>Cave cocktail</v>
       </c>
       <c r="F28">
-        <v>10437766</v>
+        <v>10446503</v>
       </c>
       <c r="G28" t="str">
-        <v>DB010126N001845</v>
+        <v>DB010126N006423</v>
       </c>
       <c r="H28" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I28" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J28" t="str">
-        <v>(blank)</v>
+        <v>Cave</v>
+      </c>
+      <c r="J28">
+        <v>777027673</v>
       </c>
       <c r="K28">
-        <v>5.317</v>
+        <v>5.24071</v>
       </c>
       <c r="L28">
-        <v>-4.08497</v>
+        <v>-3.88631</v>
       </c>
     </row>
     <row r="29">
@@ -1479,19 +1479,19 @@
         <v>46161</v>
       </c>
       <c r="C29" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>SAHI DIOMANDE</v>
       </c>
       <c r="D29" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVI.05.01</v>
       </c>
       <c r="E29" t="str">
-        <v>Chez Rebecca</v>
+        <v>CHEZ EDWIGE</v>
       </c>
       <c r="F29">
-        <v>10436601</v>
+        <v>10438216</v>
       </c>
       <c r="G29" t="str">
-        <v>DB010126N001373</v>
+        <v>DB010126N001967</v>
       </c>
       <c r="H29" t="str">
         <v>ABIDJAN</v>
@@ -1503,10 +1503,10 @@
         <v>(blank)</v>
       </c>
       <c r="K29">
-        <v>5.3358</v>
+        <v>5.33005</v>
       </c>
       <c r="L29">
-        <v>-3.94041</v>
+        <v>-4.05087</v>
       </c>
     </row>
     <row r="30">
@@ -1517,34 +1517,31 @@
         <v>46161</v>
       </c>
       <c r="C30" t="str">
-        <v>ANGELIQUE KOUASSI</v>
+        <v>Innocent Yoboue</v>
       </c>
       <c r="D30" t="str">
-        <v>ABVD.02.07</v>
+        <v>ABVI.02.05</v>
       </c>
       <c r="E30" t="str">
-        <v>Ambassade de dah</v>
+        <v>Le VITAL</v>
       </c>
       <c r="F30">
-        <v>10444168</v>
+        <v>10434178</v>
       </c>
       <c r="G30" t="str">
-        <v>DB010126N003880</v>
+        <v>DB010126N000504</v>
       </c>
       <c r="H30" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I30" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J30">
-        <v>705515208</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="K30">
-        <v>5.34111</v>
+        <v>5.29862</v>
       </c>
       <c r="L30">
-        <v>-4.07098</v>
+        <v>-3.94878</v>
       </c>
     </row>
     <row r="31">
@@ -1555,34 +1552,34 @@
         <v>46161</v>
       </c>
       <c r="C31" t="str">
-        <v>MARC AMON</v>
+        <v>SAHI DIOMANDE</v>
       </c>
       <c r="D31" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.05.01</v>
       </c>
       <c r="E31" t="str">
-        <v>Chez Eunice</v>
+        <v>Chez lidia</v>
       </c>
       <c r="F31">
-        <v>10448908</v>
+        <v>10438230</v>
       </c>
       <c r="G31" t="str">
-        <v>DB270226N006263</v>
+        <v>DB010126N001975</v>
       </c>
       <c r="H31" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I31" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J31">
-        <v>172880241</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J31" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K31">
-        <v>5.31637</v>
+        <v>5.32717</v>
       </c>
       <c r="L31">
-        <v>-4.10065</v>
+        <v>-4.05109</v>
       </c>
     </row>
     <row r="32">
@@ -1593,34 +1590,34 @@
         <v>46161</v>
       </c>
       <c r="C32" t="str">
-        <v>MARC AMON</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D32" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E32" t="str">
-        <v>VSD</v>
+        <v>CHEZ ORLY</v>
       </c>
       <c r="F32">
-        <v>10437845</v>
+        <v>10448462</v>
       </c>
       <c r="G32" t="str">
-        <v>DB010126N001867</v>
+        <v>DB010126N005908</v>
       </c>
       <c r="H32" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I32" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J32" t="str">
-        <v>(blank)</v>
+        <v>07 08 09 25 55</v>
       </c>
       <c r="K32">
-        <v>5.31552</v>
+        <v>5.37836</v>
       </c>
       <c r="L32">
-        <v>-4.08758</v>
+        <v>-3.93736</v>
       </c>
     </row>
     <row r="33">
@@ -1631,34 +1628,34 @@
         <v>46161</v>
       </c>
       <c r="C33" t="str">
-        <v>ALEXANDRE TIEGBE</v>
+        <v>SAHI DIOMANDE</v>
       </c>
       <c r="D33" t="str">
-        <v>ABVI.01.02</v>
+        <v>ABVI.05.01</v>
       </c>
       <c r="E33" t="str">
-        <v>LE POINT B</v>
+        <v>La gouro gang</v>
       </c>
       <c r="F33">
-        <v>10443674</v>
+        <v>10438291</v>
       </c>
       <c r="G33" t="str">
-        <v>DB010126N003391</v>
+        <v>DB010126N002010</v>
       </c>
       <c r="H33" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I33" t="str">
-        <v>Bar</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J33">
-        <v>575271932</v>
+        <v>103063122</v>
       </c>
       <c r="K33">
-        <v>5.43845</v>
+        <v>5.3304089</v>
       </c>
       <c r="L33">
-        <v>-4.01172</v>
+        <v>-4.0588166</v>
       </c>
     </row>
     <row r="34">
@@ -1669,19 +1666,19 @@
         <v>46161</v>
       </c>
       <c r="C34" t="str">
-        <v>EPONOH ETTIEN</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D34" t="str">
-        <v>ABVI.05.H4</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E34" t="str">
-        <v>CAVE ROUGE BLANC</v>
+        <v>La soif</v>
       </c>
       <c r="F34">
-        <v>10434312</v>
+        <v>10439475</v>
       </c>
       <c r="G34" t="str">
-        <v>DB010126N000551</v>
+        <v>DB010126N002325</v>
       </c>
       <c r="H34" t="str">
         <v>ABIDJAN</v>
@@ -1693,10 +1690,10 @@
         <v>(blank)</v>
       </c>
       <c r="K34">
-        <v>5.34012</v>
+        <v>5.3462</v>
       </c>
       <c r="L34">
-        <v>-4.10376</v>
+        <v>-3.96917</v>
       </c>
     </row>
     <row r="35">
@@ -1707,34 +1704,34 @@
         <v>46161</v>
       </c>
       <c r="C35" t="str">
-        <v>Innocent Yoboue</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D35" t="str">
-        <v>ABVI.02.05</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E35" t="str">
-        <v>Renaissance inchalla</v>
+        <v>Maquis le duo</v>
       </c>
       <c r="F35">
-        <v>10443309</v>
+        <v>10437326</v>
       </c>
       <c r="G35" t="str">
-        <v>DB010126N003392</v>
+        <v>DB010126N001739</v>
       </c>
       <c r="H35" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I35" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J35">
-        <v>140413888</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J35" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K35">
-        <v>5.29944</v>
+        <v>5.28102</v>
       </c>
       <c r="L35">
-        <v>-3.95464</v>
+        <v>-3.94628</v>
       </c>
     </row>
     <row r="36">
@@ -1745,34 +1742,34 @@
         <v>46161</v>
       </c>
       <c r="C36" t="str">
-        <v>LANDRY TIEHI</v>
+        <v>LAETITIA KISSI</v>
       </c>
       <c r="D36" t="str">
-        <v>ABVD.01.06</v>
+        <v>ABVD.02.05</v>
       </c>
       <c r="E36" t="str">
-        <v>CHEZ MAPICHOU</v>
+        <v>Maquis au rond point de SODECI</v>
       </c>
       <c r="F36">
-        <v>10437441</v>
+        <v>10450534</v>
       </c>
       <c r="G36" t="str">
-        <v>DB010126N001778</v>
+        <v>DB010126N019329</v>
       </c>
       <c r="H36" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I36" t="str">
-        <v>Maquis Choco</v>
-      </c>
-      <c r="J36" t="str">
-        <v>(blank)</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J36">
+        <v>103198583</v>
       </c>
       <c r="K36">
-        <v>5.40558</v>
+        <v>5.3243452</v>
       </c>
       <c r="L36">
-        <v>-3.98029</v>
+        <v>-4.0927375</v>
       </c>
     </row>
     <row r="37">
@@ -1783,34 +1780,34 @@
         <v>46161</v>
       </c>
       <c r="C37" t="str">
-        <v>JOSEPH ABOUA</v>
+        <v>ALEXANDRE TIEGBE</v>
       </c>
       <c r="D37" t="str">
-        <v>ABVI.03.03</v>
+        <v>ABVI.01.02</v>
       </c>
       <c r="E37" t="str">
-        <v>Cave cocktail</v>
+        <v>Chez lacost</v>
       </c>
       <c r="F37">
-        <v>10446503</v>
+        <v>10445181</v>
       </c>
       <c r="G37" t="str">
-        <v>DB010126N006423</v>
+        <v>DB010126N004226</v>
       </c>
       <c r="H37" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I37" t="str">
-        <v>Cave</v>
+        <v>Maquis</v>
       </c>
       <c r="J37">
-        <v>777027673</v>
+        <v>757009086</v>
       </c>
       <c r="K37">
-        <v>5.24071</v>
+        <v>5.43604</v>
       </c>
       <c r="L37">
-        <v>-3.88631</v>
+        <v>-4.01238</v>
       </c>
     </row>
     <row r="38">
@@ -1821,19 +1818,19 @@
         <v>46162</v>
       </c>
       <c r="C38" t="str">
-        <v>TCHESSE GOHOURE</v>
+        <v>Guy-Evrard Fodjo</v>
       </c>
       <c r="D38" t="str">
-        <v>ABVI.02.02</v>
+        <v>ABVD.02.04</v>
       </c>
       <c r="E38" t="str">
-        <v>Chez gorgi</v>
+        <v>Maquis baoulé</v>
       </c>
       <c r="F38">
-        <v>10439409</v>
+        <v>10434857</v>
       </c>
       <c r="G38" t="str">
-        <v>DB010126N002301</v>
+        <v>DB010126N000772</v>
       </c>
       <c r="H38" t="str">
         <v>ABIDJAN</v>
@@ -1845,10 +1842,10 @@
         <v>(blank)</v>
       </c>
       <c r="K38">
-        <v>5.36823</v>
+        <v>5.43034</v>
       </c>
       <c r="L38">
-        <v>-3.95773</v>
+        <v>-4.01947</v>
       </c>
     </row>
     <row r="39">
@@ -1859,34 +1856,31 @@
         <v>46162</v>
       </c>
       <c r="C39" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>Innocent Yoboue</v>
       </c>
       <c r="D39" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVI.02.05</v>
       </c>
       <c r="E39" t="str">
-        <v>Bar Franc Suisse</v>
+        <v>Maquis relaxe</v>
       </c>
       <c r="F39">
-        <v>10435863</v>
+        <v>10434242</v>
       </c>
       <c r="G39" t="str">
-        <v>DB010126N001162</v>
+        <v>DB010126N000529</v>
       </c>
       <c r="H39" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I39" t="str">
-        <v>Bar</v>
-      </c>
-      <c r="J39">
-        <v>708465441</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="K39">
-        <v>5.30073</v>
+        <v>5.29552</v>
       </c>
       <c r="L39">
-        <v>-3.97722</v>
+        <v>-3.95666</v>
       </c>
     </row>
     <row r="40">
@@ -1903,28 +1897,28 @@
         <v>ABVI.01.02</v>
       </c>
       <c r="E40" t="str">
-        <v>Chez Madame boka</v>
+        <v>Chez Luc</v>
       </c>
       <c r="F40">
-        <v>10432888</v>
+        <v>10445441</v>
       </c>
       <c r="G40" t="str">
-        <v>DB010126N007406</v>
+        <v>DB010126N004486</v>
       </c>
       <c r="H40" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I40" t="str">
-        <v>Cave - On</v>
-      </c>
-      <c r="J40" t="str">
-        <v>(blank)</v>
+        <v>Maquis</v>
+      </c>
+      <c r="J40">
+        <v>502544450</v>
       </c>
       <c r="K40">
-        <v>5.4352</v>
+        <v>5.43372</v>
       </c>
       <c r="L40">
-        <v>-4.01047</v>
+        <v>-4.0185</v>
       </c>
     </row>
     <row r="41">
@@ -1935,19 +1929,19 @@
         <v>46162</v>
       </c>
       <c r="C41" t="str">
-        <v>EPONOH ETTIEN</v>
+        <v>LAETITIA KISSI</v>
       </c>
       <c r="D41" t="str">
-        <v>ABVI.05.H4</v>
+        <v>ABVD.02.05</v>
       </c>
       <c r="E41" t="str">
-        <v>Espace BONOUA</v>
+        <v>CHEZ LE ROI ZULU</v>
       </c>
       <c r="F41">
-        <v>10434356</v>
+        <v>10437013</v>
       </c>
       <c r="G41" t="str">
-        <v>DB010126N000568</v>
+        <v>DB010126N001580</v>
       </c>
       <c r="H41" t="str">
         <v>ABIDJAN</v>
@@ -1959,10 +1953,10 @@
         <v>(blank)</v>
       </c>
       <c r="K41">
-        <v>5.34022</v>
+        <v>5.3638</v>
       </c>
       <c r="L41">
-        <v>-4.10791</v>
+        <v>-4.0942</v>
       </c>
     </row>
     <row r="42">
@@ -1973,19 +1967,19 @@
         <v>46162</v>
       </c>
       <c r="C42" t="str">
-        <v>Guy-Evrard Fodjo</v>
+        <v>FRANCK YAO</v>
       </c>
       <c r="D42" t="str">
-        <v>ABVD.02.04</v>
+        <v>ABVI.03.02</v>
       </c>
       <c r="E42" t="str">
-        <v>3 EME PONT</v>
+        <v>Buvette Emmanuel</v>
       </c>
       <c r="F42">
-        <v>10446528</v>
+        <v>10446536</v>
       </c>
       <c r="G42" t="str">
-        <v>DB010126N005464</v>
+        <v>DB010126N005472</v>
       </c>
       <c r="H42" t="str">
         <v>ABIDJAN</v>
@@ -1994,13 +1988,13 @@
         <v>Maquis</v>
       </c>
       <c r="J42">
-        <v>171532071</v>
+        <v>707992828</v>
       </c>
       <c r="K42">
-        <v>5.4148</v>
+        <v>5.24264</v>
       </c>
       <c r="L42">
-        <v>-4.03342</v>
+        <v>-3.91516</v>
       </c>
     </row>
     <row r="43">
@@ -2011,34 +2005,34 @@
         <v>46162</v>
       </c>
       <c r="C43" t="str">
-        <v>LAETITIA KISSI</v>
+        <v>HERMANN GOGOUA</v>
       </c>
       <c r="D43" t="str">
-        <v>ABVD.02.05</v>
+        <v>ABVI.04.02</v>
       </c>
       <c r="E43" t="str">
-        <v>Vector VIP</v>
+        <v>Chez vigo</v>
       </c>
       <c r="F43">
-        <v>10443547</v>
+        <v>10449639</v>
       </c>
       <c r="G43" t="str">
-        <v>DB010126N003263</v>
+        <v>DB010126N015746</v>
       </c>
       <c r="H43" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I43" t="str">
-        <v>Maquis</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J43">
-        <v>707293848</v>
+        <v>709274952</v>
       </c>
       <c r="K43">
-        <v>5.32568</v>
+        <v>5.3596849</v>
       </c>
       <c r="L43">
-        <v>-4.0924</v>
+        <v>-3.9470836</v>
       </c>
     </row>
     <row r="44">
@@ -2049,34 +2043,34 @@
         <v>46162</v>
       </c>
       <c r="C44" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D44" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E44" t="str">
-        <v>La maison mère</v>
+        <v>POINT VIRGULE</v>
       </c>
       <c r="F44">
-        <v>10438293</v>
+        <v>10448475</v>
       </c>
       <c r="G44" t="str">
-        <v>DB010126N002012</v>
+        <v>DB010126N005921</v>
       </c>
       <c r="H44" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I44" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J44" t="str">
-        <v>(blank)</v>
+        <v>07 09 82 53 80</v>
       </c>
       <c r="K44">
-        <v>5.3353</v>
+        <v>5.36307</v>
       </c>
       <c r="L44">
-        <v>-4.03847</v>
+        <v>-3.8996</v>
       </c>
     </row>
     <row r="45">
@@ -2087,34 +2081,34 @@
         <v>46162</v>
       </c>
       <c r="C45" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D45" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E45" t="str">
-        <v>Côté d Ivoire Burkina</v>
+        <v>Abidjan paris</v>
       </c>
       <c r="F45">
-        <v>10434561</v>
+        <v>10437184</v>
       </c>
       <c r="G45" t="str">
-        <v>DB010126N000663</v>
+        <v>DB010126N001661</v>
       </c>
       <c r="H45" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I45" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis Choco</v>
       </c>
       <c r="J45" t="str">
         <v>(blank)</v>
       </c>
       <c r="K45">
-        <v>5.37323</v>
+        <v>5.25865</v>
       </c>
       <c r="L45">
-        <v>-4.00604</v>
+        <v>-3.96823</v>
       </c>
     </row>
     <row r="46">
@@ -2131,28 +2125,28 @@
         <v>ABVI.03.03</v>
       </c>
       <c r="E46" t="str">
-        <v>After work cave restaurant</v>
+        <v>Bar Cœur  blanc  vip</v>
       </c>
       <c r="F46">
-        <v>10444967</v>
+        <v>10443432</v>
       </c>
       <c r="G46" t="str">
-        <v>DB010126N004153</v>
+        <v>DB010126N003150</v>
       </c>
       <c r="H46" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I46" t="str">
-        <v>Maquis</v>
+        <v>Bar</v>
       </c>
       <c r="J46">
-        <v>797631812</v>
+        <v>140040137</v>
       </c>
       <c r="K46">
-        <v>5.23696</v>
+        <v>5.2637</v>
       </c>
       <c r="L46">
-        <v>-3.87626</v>
+        <v>-3.9005</v>
       </c>
     </row>
     <row r="47">
@@ -2163,34 +2157,34 @@
         <v>46162</v>
       </c>
       <c r="C47" t="str">
-        <v>Guy-Evrard Fodjo</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D47" t="str">
-        <v>ABVD.02.04</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E47" t="str">
-        <v>BEST FORT</v>
+        <v>Maquis universel</v>
       </c>
       <c r="F47">
-        <v>10445201</v>
+        <v>10437351</v>
       </c>
       <c r="G47" t="str">
-        <v>DB010126N004246</v>
+        <v>DB010126N001753</v>
       </c>
       <c r="H47" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I47" t="str">
-        <v>Cave</v>
-      </c>
-      <c r="J47">
-        <v>797344078</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J47" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K47">
-        <v>5.4398</v>
+        <v>5.2544</v>
       </c>
       <c r="L47">
-        <v>-4.02256</v>
+        <v>-3.96511</v>
       </c>
     </row>
     <row r="48">
@@ -2201,34 +2195,34 @@
         <v>46162</v>
       </c>
       <c r="C48" t="str">
-        <v>LANDRY TIEHI</v>
+        <v>Guy-Evrard Fodjo</v>
       </c>
       <c r="D48" t="str">
-        <v>ABVD.01.06</v>
+        <v>ABVD.02.04</v>
       </c>
       <c r="E48" t="str">
-        <v>Maqui espace sans bruit</v>
+        <v>BEST FORT</v>
       </c>
       <c r="F48">
-        <v>10437520</v>
+        <v>10445201</v>
       </c>
       <c r="G48" t="str">
-        <v>DB010126N001797</v>
+        <v>DB010126N004246</v>
       </c>
       <c r="H48" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I48" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J48" t="str">
-        <v>(blank)</v>
+        <v>Cave</v>
+      </c>
+      <c r="J48">
+        <v>797344078</v>
       </c>
       <c r="K48">
-        <v>5.42515</v>
+        <v>5.4398</v>
       </c>
       <c r="L48">
-        <v>-3.97867</v>
+        <v>-4.02256</v>
       </c>
     </row>
     <row r="49">
@@ -2239,34 +2233,34 @@
         <v>46162</v>
       </c>
       <c r="C49" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>ANGELIQUE KOUASSI</v>
       </c>
       <c r="D49" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVD.02.07</v>
       </c>
       <c r="E49" t="str">
-        <v>Bar magnum</v>
+        <v>Chez la mère</v>
       </c>
       <c r="F49">
-        <v>10446857</v>
+        <v>10433284</v>
       </c>
       <c r="G49" t="str">
-        <v>DB010126N005746</v>
+        <v>DB010126N000182</v>
       </c>
       <c r="H49" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I49" t="str">
-        <v>Bar</v>
-      </c>
-      <c r="J49">
-        <v>708531706</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J49" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K49">
-        <v>5.32479</v>
+        <v>5.33981</v>
       </c>
       <c r="L49">
-        <v>-3.95325</v>
+        <v>-4.06751</v>
       </c>
     </row>
     <row r="50">
@@ -2277,19 +2271,19 @@
         <v>46163</v>
       </c>
       <c r="C50" t="str">
-        <v>MARC AMON</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D50" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E50" t="str">
-        <v>Chez makambo</v>
+        <v>Maquis JazzMento</v>
       </c>
       <c r="F50">
-        <v>10444222</v>
+        <v>10443825</v>
       </c>
       <c r="G50" t="str">
-        <v>DB010126N003934</v>
+        <v>DB010126N003539</v>
       </c>
       <c r="H50" t="str">
         <v>ABIDJAN</v>
@@ -2298,13 +2292,13 @@
         <v>Maquis</v>
       </c>
       <c r="J50">
-        <v>708037090</v>
+        <v>709202142</v>
       </c>
       <c r="K50">
-        <v>5.31923</v>
+        <v>5.34889</v>
       </c>
       <c r="L50">
-        <v>-4.10032</v>
+        <v>-3.97443</v>
       </c>
     </row>
     <row r="51">
@@ -2315,34 +2309,34 @@
         <v>46163</v>
       </c>
       <c r="C51" t="str">
-        <v>LAFALI KONE</v>
+        <v>EULOGE ESSIS</v>
       </c>
       <c r="D51" t="str">
-        <v>ABVI.02.03</v>
+        <v>ABVD.01.04</v>
       </c>
       <c r="E51" t="str">
-        <v>Chez l'Honorable</v>
+        <v>Maquis bon prix</v>
       </c>
       <c r="F51">
-        <v>10437224</v>
+        <v>10434634</v>
       </c>
       <c r="G51" t="str">
-        <v>DB010126N001685</v>
+        <v>DB010126N000700</v>
       </c>
       <c r="H51" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I51" t="str">
-        <v>Maquis Choco</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J51" t="str">
         <v>(blank)</v>
       </c>
       <c r="K51">
-        <v>5.25787</v>
+        <v>5.36661</v>
       </c>
       <c r="L51">
-        <v>-3.95962</v>
+        <v>-4.00814</v>
       </c>
     </row>
     <row r="52">
@@ -2353,34 +2347,34 @@
         <v>46163</v>
       </c>
       <c r="C52" t="str">
-        <v>ALEXANDRE TIEGBE</v>
+        <v>Innocent Yoboue</v>
       </c>
       <c r="D52" t="str">
-        <v>ABVI.01.02</v>
+        <v>ABVI.02.05</v>
       </c>
       <c r="E52" t="str">
-        <v>Top 14</v>
+        <v>Guide à gauche</v>
       </c>
       <c r="F52">
-        <v>10445516</v>
+        <v>10443305</v>
       </c>
       <c r="G52" t="str">
-        <v>DB010126N004560</v>
+        <v>DB010126N003017</v>
       </c>
       <c r="H52" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I52" t="str">
-        <v>Maquis</v>
+        <v>Cave</v>
       </c>
       <c r="J52">
-        <v>758487442</v>
+        <v>749638870</v>
       </c>
       <c r="K52">
-        <v>5.41906</v>
+        <v>5.2961</v>
       </c>
       <c r="L52">
-        <v>-3.99084</v>
+        <v>-3.9565</v>
       </c>
     </row>
     <row r="53">
@@ -2391,34 +2385,34 @@
         <v>46163</v>
       </c>
       <c r="C53" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>ANGELIQUE KOUASSI</v>
       </c>
       <c r="D53" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVD.02.07</v>
       </c>
       <c r="E53" t="str">
-        <v>Restaurant dinasty</v>
+        <v>La terrasse</v>
       </c>
       <c r="F53">
-        <v>10444815</v>
+        <v>10433344</v>
       </c>
       <c r="G53" t="str">
-        <v>DB010126N004004</v>
+        <v>DB010126N000201</v>
       </c>
       <c r="H53" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I53" t="str">
-        <v>Restaurant</v>
-      </c>
-      <c r="J53">
-        <v>779765999</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J53" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K53">
-        <v>5.3221</v>
+        <v>5.33095</v>
       </c>
       <c r="L53">
-        <v>-4.04447</v>
+        <v>-4.07141</v>
       </c>
     </row>
     <row r="54">
@@ -2429,34 +2423,34 @@
         <v>46163</v>
       </c>
       <c r="C54" t="str">
-        <v>TCHESSE GOHOURE</v>
+        <v>EPONOH ETTIEN</v>
       </c>
       <c r="D54" t="str">
-        <v>ABVI.02.02</v>
+        <v>ABVI.05.H4</v>
       </c>
       <c r="E54" t="str">
-        <v>L'o vive</v>
+        <v>Cave le Nil</v>
       </c>
       <c r="F54">
-        <v>10449703</v>
+        <v>10434307</v>
       </c>
       <c r="G54" t="str">
-        <v>DB010126N018625</v>
+        <v>DB010126N007199</v>
       </c>
       <c r="H54" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I54" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J54">
-        <v>153210318</v>
+        <v>Cave - On</v>
+      </c>
+      <c r="J54" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K54">
-        <v>5.3536467</v>
+        <v>5.32814</v>
       </c>
       <c r="L54">
-        <v>-3.9584083</v>
+        <v>-4.09926</v>
       </c>
     </row>
     <row r="55">
@@ -2467,34 +2461,34 @@
         <v>46163</v>
       </c>
       <c r="C55" t="str">
-        <v>AMINE COULIBALY</v>
+        <v>Guy-Evrard Fodjo</v>
       </c>
       <c r="D55" t="str">
-        <v>ABVD.01.01</v>
+        <v>ABVD.02.04</v>
       </c>
       <c r="E55" t="str">
-        <v>Chez Françoise</v>
+        <v>Cave TIKTOK</v>
       </c>
       <c r="F55">
-        <v>10433072</v>
+        <v>10434753</v>
       </c>
       <c r="G55" t="str">
-        <v>DB010126N000096</v>
+        <v>DB010126N000746</v>
       </c>
       <c r="H55" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I55" t="str">
-        <v>Maquis Choco</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J55" t="str">
         <v>(blank)</v>
       </c>
       <c r="K55">
-        <v>5.34238</v>
+        <v>5.43879</v>
       </c>
       <c r="L55">
-        <v>-4.0224</v>
+        <v>-4.02576</v>
       </c>
     </row>
     <row r="56">
@@ -2505,19 +2499,19 @@
         <v>46163</v>
       </c>
       <c r="C56" t="str">
-        <v>ANGELIQUE KOUASSI</v>
+        <v>FRANCK KOUADIO</v>
       </c>
       <c r="D56" t="str">
-        <v>ABVD.02.07</v>
+        <v>ABVD.02.03</v>
       </c>
       <c r="E56" t="str">
-        <v>Maquis Palais</v>
+        <v>Cave Emmanuel</v>
       </c>
       <c r="F56">
-        <v>10446668</v>
+        <v>10443583</v>
       </c>
       <c r="G56" t="str">
-        <v>DB010126N006441</v>
+        <v>DB010126N003299</v>
       </c>
       <c r="H56" t="str">
         <v>ABIDJAN</v>
@@ -2526,13 +2520,13 @@
         <v>Maquis</v>
       </c>
       <c r="J56">
-        <v>707083098</v>
+        <v>709362201</v>
       </c>
       <c r="K56">
-        <v>5.3253</v>
+        <v>5.332055</v>
       </c>
       <c r="L56">
-        <v>-4.07759</v>
+        <v>-4.112239</v>
       </c>
     </row>
     <row r="57">
@@ -2543,19 +2537,19 @@
         <v>46163</v>
       </c>
       <c r="C57" t="str">
-        <v>AMINE COULIBALY</v>
+        <v>FRANCK YAO</v>
       </c>
       <c r="D57" t="str">
-        <v>ABVD.01.01</v>
+        <v>ABVI.03.02</v>
       </c>
       <c r="E57" t="str">
-        <v>Maquis effrasie</v>
+        <v>Air port dabali</v>
       </c>
       <c r="F57">
-        <v>10433166</v>
+        <v>10435346</v>
       </c>
       <c r="G57" t="str">
-        <v>DB010126N000138</v>
+        <v>DB010126N000925</v>
       </c>
       <c r="H57" t="str">
         <v>ABIDJAN</v>
@@ -2567,10 +2561,10 @@
         <v>(blank)</v>
       </c>
       <c r="K57">
-        <v>5.35877</v>
+        <v>5.25312</v>
       </c>
       <c r="L57">
-        <v>-4.02973</v>
+        <v>-3.93477</v>
       </c>
     </row>
     <row r="58">
@@ -2581,34 +2575,34 @@
         <v>46163</v>
       </c>
       <c r="C58" t="str">
-        <v>EPONOH ETTIEN</v>
+        <v>AMINE COULIBALY</v>
       </c>
       <c r="D58" t="str">
-        <v>ABVI.05.H4</v>
+        <v>ABVD.01.01</v>
       </c>
       <c r="E58" t="str">
-        <v>ESPACE MOAYE</v>
+        <v>Maquis Bordelaise</v>
       </c>
       <c r="F58">
-        <v>10443570</v>
+        <v>10433147</v>
       </c>
       <c r="G58" t="str">
-        <v>DB010126N003286</v>
+        <v>DB010126N000130</v>
       </c>
       <c r="H58" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I58" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J58">
-        <v>7496595511</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J58" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K58">
-        <v>5.34111</v>
+        <v>5.34684</v>
       </c>
       <c r="L58">
-        <v>-4.09853</v>
+        <v>-4.03469</v>
       </c>
     </row>
     <row r="59">
@@ -2619,34 +2613,34 @@
         <v>46163</v>
       </c>
       <c r="C59" t="str">
-        <v>MARC AMON</v>
+        <v>EPONOH ETTIEN</v>
       </c>
       <c r="D59" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.05.H4</v>
       </c>
       <c r="E59" t="str">
-        <v>Abidjan Continue</v>
+        <v>Cave du bonheur</v>
       </c>
       <c r="F59">
-        <v>10444193</v>
+        <v>10450144</v>
       </c>
       <c r="G59" t="str">
-        <v>DB010126N003905</v>
+        <v>DB010126N008943</v>
       </c>
       <c r="H59" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I59" t="str">
-        <v>Maquis</v>
+        <v>Cave</v>
       </c>
       <c r="J59">
-        <v>506955151</v>
+        <v>101114621</v>
       </c>
       <c r="K59">
-        <v>5.31918</v>
+        <v>5.3413798</v>
       </c>
       <c r="L59">
-        <v>-4.08031</v>
+        <v>-4.0981519</v>
       </c>
     </row>
     <row r="60">
@@ -2657,19 +2651,19 @@
         <v>46163</v>
       </c>
       <c r="C60" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>JOSEPH ABOUA</v>
       </c>
       <c r="D60" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVI.03.03</v>
       </c>
       <c r="E60" t="str">
-        <v>Les retrouvailles</v>
+        <v>Marquis joli bébé</v>
       </c>
       <c r="F60">
-        <v>10434616</v>
+        <v>10436525</v>
       </c>
       <c r="G60" t="str">
-        <v>DB010126N000689</v>
+        <v>DB010126N001347</v>
       </c>
       <c r="H60" t="str">
         <v>ABIDJAN</v>
@@ -2681,10 +2675,10 @@
         <v>(blank)</v>
       </c>
       <c r="K60">
-        <v>5.37127</v>
+        <v>5.24013</v>
       </c>
       <c r="L60">
-        <v>-3.9998</v>
+        <v>-3.88094</v>
       </c>
     </row>
     <row r="61">
@@ -2695,19 +2689,19 @@
         <v>46163</v>
       </c>
       <c r="C61" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>ALEXANDRE TIEGBE</v>
       </c>
       <c r="D61" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVI.01.02</v>
       </c>
       <c r="E61" t="str">
-        <v>MAQUIS ROYAL</v>
+        <v>Chez Honoré</v>
       </c>
       <c r="F61">
-        <v>10434677</v>
+        <v>10432885</v>
       </c>
       <c r="G61" t="str">
-        <v>DB010126N000721</v>
+        <v>DB010126N000031</v>
       </c>
       <c r="H61" t="str">
         <v>ABIDJAN</v>
@@ -2719,10 +2713,10 @@
         <v>(blank)</v>
       </c>
       <c r="K61">
-        <v>5.37097</v>
+        <v>5.41527</v>
       </c>
       <c r="L61">
-        <v>-4.00108</v>
+        <v>-4.00187</v>
       </c>
     </row>
     <row r="62">
@@ -2733,19 +2727,19 @@
         <v>46165</v>
       </c>
       <c r="C62" t="str">
-        <v>AIME KONAN</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D62" t="str">
-        <v>ABVI.04.04</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E62" t="str">
-        <v>Ambassade</v>
+        <v>Maquis C</v>
       </c>
       <c r="F62">
-        <v>10439781</v>
+        <v>10437294</v>
       </c>
       <c r="G62" t="str">
-        <v>DB010126N007180</v>
+        <v>DB010126N001724</v>
       </c>
       <c r="H62" t="str">
         <v>ABIDJAN</v>
@@ -2757,10 +2751,10 @@
         <v>(blank)</v>
       </c>
       <c r="K62">
-        <v>5.39345</v>
+        <v>5.26622</v>
       </c>
       <c r="L62">
-        <v>-3.85496</v>
+        <v>-3.98773</v>
       </c>
     </row>
     <row r="63">
@@ -2771,19 +2765,19 @@
         <v>46165</v>
       </c>
       <c r="C63" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>ANGELIQUE KOUASSI</v>
       </c>
       <c r="D63" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVD.02.07</v>
       </c>
       <c r="E63" t="str">
-        <v>Petit Paris</v>
+        <v>Chez maman ebongo</v>
       </c>
       <c r="F63">
-        <v>10438360</v>
+        <v>10449412</v>
       </c>
       <c r="G63" t="str">
-        <v>DB010126N002054</v>
+        <v>DB010126N014745</v>
       </c>
       <c r="H63" t="str">
         <v>ABIDJAN</v>
@@ -2792,13 +2786,13 @@
         <v>Maquis Standard</v>
       </c>
       <c r="J63">
-        <v>749279492</v>
+        <v>757525299</v>
       </c>
       <c r="K63">
-        <v>5.3086283</v>
+        <v>5.3089102</v>
       </c>
       <c r="L63">
-        <v>-4.038045</v>
+        <v>-4.0455843</v>
       </c>
     </row>
     <row r="64">
@@ -2809,34 +2803,34 @@
         <v>46165</v>
       </c>
       <c r="C64" t="str">
-        <v>JOSEPH ABOUA</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D64" t="str">
-        <v>ABVI.03.03</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E64" t="str">
-        <v>L'espace univers</v>
+        <v>Bar twins</v>
       </c>
       <c r="F64">
-        <v>10436487</v>
+        <v>10449990</v>
       </c>
       <c r="G64" t="str">
-        <v>DB010126N001337</v>
+        <v>DB010126N011349</v>
       </c>
       <c r="H64" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I64" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J64" t="str">
-        <v>(blank)</v>
+        <v>Bar Standard</v>
+      </c>
+      <c r="J64">
+        <v>574037587</v>
       </c>
       <c r="K64">
-        <v>5.26908</v>
+        <v>5.2663635</v>
       </c>
       <c r="L64">
-        <v>-3.89212</v>
+        <v>-3.9851321</v>
       </c>
     </row>
     <row r="65">
@@ -2847,19 +2841,19 @@
         <v>46165</v>
       </c>
       <c r="C65" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>LANDRY TIEHI</v>
       </c>
       <c r="D65" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVD.01.06</v>
       </c>
       <c r="E65" t="str">
-        <v>Moto moto</v>
+        <v>Maqui bleu blanc</v>
       </c>
       <c r="F65">
-        <v>10434684</v>
+        <v>10449669</v>
       </c>
       <c r="G65" t="str">
-        <v>DB010126N000724</v>
+        <v>DB010126N018835</v>
       </c>
       <c r="H65" t="str">
         <v>ABIDJAN</v>
@@ -2867,14 +2861,14 @@
       <c r="I65" t="str">
         <v>Maquis Standard</v>
       </c>
-      <c r="J65" t="str">
-        <v>(blank)</v>
+      <c r="J65">
+        <v>584909739</v>
       </c>
       <c r="K65">
-        <v>5.3684</v>
+        <v>5.4048764</v>
       </c>
       <c r="L65">
-        <v>-4.00251</v>
+        <v>-3.9593527</v>
       </c>
     </row>
     <row r="66">
@@ -2885,19 +2879,19 @@
         <v>46165</v>
       </c>
       <c r="C66" t="str">
-        <v>MARC AMON</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D66" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E66" t="str">
-        <v>Maquis au plan B</v>
+        <v>Maquis Rio de Janeiro</v>
       </c>
       <c r="F66">
-        <v>10437753</v>
+        <v>10437346</v>
       </c>
       <c r="G66" t="str">
-        <v>DB010126N001840</v>
+        <v>DB010126N001749</v>
       </c>
       <c r="H66" t="str">
         <v>ABIDJAN</v>
@@ -2909,10 +2903,10 @@
         <v>(blank)</v>
       </c>
       <c r="K66">
-        <v>5.32182</v>
+        <v>5.2529</v>
       </c>
       <c r="L66">
-        <v>-4.08083</v>
+        <v>-4.00145</v>
       </c>
     </row>
     <row r="67">
@@ -2923,19 +2917,19 @@
         <v>46165</v>
       </c>
       <c r="C67" t="str">
-        <v>ANGELIQUE KOUASSI</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D67" t="str">
-        <v>ABVD.02.07</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E67" t="str">
-        <v>Chez maman ebongo</v>
+        <v>CONNEXION</v>
       </c>
       <c r="F67">
-        <v>10449412</v>
+        <v>10449426</v>
       </c>
       <c r="G67" t="str">
-        <v>DB010126N014745</v>
+        <v>DB010126N013457</v>
       </c>
       <c r="H67" t="str">
         <v>ABIDJAN</v>
@@ -2944,13 +2938,13 @@
         <v>Maquis Standard</v>
       </c>
       <c r="J67">
-        <v>757525299</v>
+        <v>101047238</v>
       </c>
       <c r="K67">
-        <v>5.3089102</v>
+        <v>5.349204</v>
       </c>
       <c r="L67">
-        <v>-4.0455843</v>
+        <v>-3.8872972</v>
       </c>
     </row>
     <row r="68">
@@ -2961,34 +2955,34 @@
         <v>46165</v>
       </c>
       <c r="C68" t="str">
-        <v>TCHESSE GOHOURE</v>
+        <v>ANGELIQUE KOUASSI</v>
       </c>
       <c r="D68" t="str">
-        <v>ABVI.02.02</v>
+        <v>ABVD.02.07</v>
       </c>
       <c r="E68" t="str">
-        <v>Chili Vibes</v>
+        <v>Penalty penalty</v>
       </c>
       <c r="F68">
-        <v>10442766</v>
+        <v>10450523</v>
       </c>
       <c r="G68" t="str">
-        <v>DB010126N002486</v>
+        <v>DB010126N022969</v>
       </c>
       <c r="H68" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I68" t="str">
-        <v>Restaurant</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J68">
-        <v>787738178</v>
+        <v>546403601</v>
       </c>
       <c r="K68">
-        <v>5.34675</v>
+        <v>5.307884</v>
       </c>
       <c r="L68">
-        <v>-3.96938</v>
+        <v>-4.0449441</v>
       </c>
     </row>
     <row r="69">
@@ -2999,19 +2993,19 @@
         <v>46165</v>
       </c>
       <c r="C69" t="str">
-        <v>FRANCK KOUADIO</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D69" t="str">
-        <v>ABVD.02.03</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E69" t="str">
-        <v>CAVE CHEZ MAMAN BLANCHO</v>
+        <v>Petit animaux</v>
       </c>
       <c r="F69">
-        <v>10450275</v>
+        <v>10450009</v>
       </c>
       <c r="G69" t="str">
-        <v>DB010126N012217</v>
+        <v>DB010126N022980</v>
       </c>
       <c r="H69" t="str">
         <v>ABIDJAN</v>
@@ -3020,13 +3014,13 @@
         <v>Maquis Standard</v>
       </c>
       <c r="J69">
-        <v>102555370</v>
+        <v>556363121</v>
       </c>
       <c r="K69">
-        <v>5.351587</v>
+        <v>5.25578</v>
       </c>
       <c r="L69">
-        <v>-4.1095397</v>
+        <v>-3.9601933</v>
       </c>
     </row>
     <row r="70">
@@ -3037,34 +3031,34 @@
         <v>46165</v>
       </c>
       <c r="C70" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>FRANCK KOUADIO</v>
       </c>
       <c r="D70" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVD.02.03</v>
       </c>
       <c r="E70" t="str">
-        <v>Maquis piment dans yeux</v>
+        <v>Maquis baoulé</v>
       </c>
       <c r="F70">
-        <v>10438349</v>
+        <v>10444819</v>
       </c>
       <c r="G70" t="str">
-        <v>DB010126N002050</v>
+        <v>DB010126N004008</v>
       </c>
       <c r="H70" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I70" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J70">
-        <v>504524322</v>
+        <v>710735451</v>
       </c>
       <c r="K70">
-        <v>5.3304707</v>
+        <v>5.35118</v>
       </c>
       <c r="L70">
-        <v>-4.0581602</v>
+        <v>-4.10952</v>
       </c>
     </row>
     <row r="71">
@@ -3075,34 +3069,34 @@
         <v>46165</v>
       </c>
       <c r="C71" t="str">
-        <v>FRANCK KOUADIO</v>
+        <v>FRANCK YAO</v>
       </c>
       <c r="D71" t="str">
-        <v>ABVD.02.03</v>
+        <v>ABVI.03.02</v>
       </c>
       <c r="E71" t="str">
-        <v>Le Royaume VIP</v>
+        <v>Prestige bar</v>
       </c>
       <c r="F71">
-        <v>10444812</v>
+        <v>10446647</v>
       </c>
       <c r="G71" t="str">
-        <v>DB010126N004001</v>
+        <v>DB010126N005583</v>
       </c>
       <c r="H71" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I71" t="str">
-        <v>Maquis</v>
+        <v>Bar</v>
       </c>
       <c r="J71">
-        <v>708986328</v>
+        <v>545370101</v>
       </c>
       <c r="K71">
-        <v>5.35018</v>
+        <v>5.27484</v>
       </c>
       <c r="L71">
-        <v>-4.10754</v>
+        <v>-3.95386</v>
       </c>
     </row>
     <row r="72">
@@ -3113,34 +3107,34 @@
         <v>46165</v>
       </c>
       <c r="C72" t="str">
-        <v>LAETITIA KISSI</v>
+        <v>HERMANN GOGOUA</v>
       </c>
       <c r="D72" t="str">
-        <v>ABVD.02.05</v>
+        <v>ABVI.04.02</v>
       </c>
       <c r="E72" t="str">
-        <v>Chez cacachi</v>
+        <v>chez Mimi</v>
       </c>
       <c r="F72">
-        <v>10450299</v>
+        <v>10449719</v>
       </c>
       <c r="G72" t="str">
-        <v>DB010126N013641</v>
+        <v>DB010126N011170</v>
       </c>
       <c r="H72" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I72" t="str">
-        <v>Maquis Standard</v>
+        <v>MAQUIS RESTAURANT</v>
       </c>
       <c r="J72">
-        <v>545252875</v>
+        <v>102201016</v>
       </c>
       <c r="K72">
-        <v>5.3531924</v>
+        <v>5.3738422</v>
       </c>
       <c r="L72">
-        <v>-4.0751042</v>
+        <v>-3.9557372</v>
       </c>
     </row>
     <row r="73">
@@ -3157,28 +3151,28 @@
         <v>ABVD.01.06</v>
       </c>
       <c r="E73" t="str">
-        <v>Chez joyce</v>
+        <v>Chez clementine</v>
       </c>
       <c r="F73">
-        <v>10446880</v>
+        <v>10449660</v>
       </c>
       <c r="G73" t="str">
-        <v>DB010126N005769</v>
+        <v>DB010126N013753</v>
       </c>
       <c r="H73" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I73" t="str">
-        <v>Maquis</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J73">
-        <v>719793364</v>
+        <v>152016252</v>
       </c>
       <c r="K73">
-        <v>5.41524</v>
+        <v>5.4046869</v>
       </c>
       <c r="L73">
-        <v>-3.963</v>
+        <v>-3.9590465</v>
       </c>
     </row>
     <row r="74">
@@ -3189,34 +3183,34 @@
         <v>46167</v>
       </c>
       <c r="C74" t="str">
-        <v>JOSEPH ABOUA</v>
+        <v>SAHI DIOMANDE</v>
       </c>
       <c r="D74" t="str">
-        <v>ABVI.03.03</v>
+        <v>ABVI.05.01</v>
       </c>
       <c r="E74" t="str">
-        <v>Maquis restaurant chez rose</v>
+        <v>Terre d'Afrique</v>
       </c>
       <c r="F74">
-        <v>10450010</v>
+        <v>10438378</v>
       </c>
       <c r="G74" t="str">
-        <v>DB010126N021672</v>
+        <v>DB010126N002064</v>
       </c>
       <c r="H74" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I74" t="str">
-        <v>MAQUIS RESTAURANT</v>
+        <v>Maquis Choco</v>
       </c>
       <c r="J74">
-        <v>709166454</v>
+        <v>758659347</v>
       </c>
       <c r="K74">
-        <v>5.2401328</v>
+        <v>5.3457074</v>
       </c>
       <c r="L74">
-        <v>-3.8740864</v>
+        <v>-4.0592417</v>
       </c>
     </row>
     <row r="75">
@@ -3227,34 +3221,34 @@
         <v>46167</v>
       </c>
       <c r="C75" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D75" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E75" t="str">
-        <v>Maquis chez felicité</v>
+        <v>Continental Grill</v>
       </c>
       <c r="F75">
-        <v>10449616</v>
+        <v>10449710</v>
       </c>
       <c r="G75" t="str">
-        <v>DB010126N006459</v>
+        <v>DB010126N015978</v>
       </c>
       <c r="H75" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I75" t="str">
-        <v>Maquis Standard</v>
+        <v>Restaurant Standard</v>
       </c>
       <c r="J75">
-        <v>172266567</v>
+        <v>702816284</v>
       </c>
       <c r="K75">
-        <v>5.3465109</v>
+        <v>5.3602276</v>
       </c>
       <c r="L75">
-        <v>-3.9448892</v>
+        <v>-3.9258822</v>
       </c>
     </row>
     <row r="76">
@@ -3265,34 +3259,34 @@
         <v>46167</v>
       </c>
       <c r="C76" t="str">
-        <v>ANGELIQUE KOUASSI</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D76" t="str">
-        <v>ABVD.02.07</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E76" t="str">
-        <v>Gris blanc</v>
+        <v>BRAZILIA CAVE</v>
       </c>
       <c r="F76">
-        <v>10444868</v>
+        <v>10449690</v>
       </c>
       <c r="G76" t="str">
-        <v>DB010126N004054</v>
+        <v>DB010126N011665</v>
       </c>
       <c r="H76" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I76" t="str">
-        <v>Maquis</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J76">
-        <v>759589598</v>
+        <v>576055851</v>
       </c>
       <c r="K76">
-        <v>5.35339</v>
+        <v>5.3497964</v>
       </c>
       <c r="L76">
-        <v>-4.07288</v>
+        <v>-3.9676602</v>
       </c>
     </row>
     <row r="77">
@@ -3303,34 +3297,34 @@
         <v>46167</v>
       </c>
       <c r="C77" t="str">
-        <v>ALEXANDRE TIEGBE</v>
+        <v>Guy-Evrard Fodjo</v>
       </c>
       <c r="D77" t="str">
-        <v>ABVI.01.02</v>
+        <v>ABVD.02.04</v>
       </c>
       <c r="E77" t="str">
-        <v>Cave des 3 abres</v>
+        <v>Campement</v>
       </c>
       <c r="F77">
-        <v>10432862</v>
+        <v>10446587</v>
       </c>
       <c r="G77" t="str">
-        <v>DB010126N000024</v>
+        <v>DB010126N005521</v>
       </c>
       <c r="H77" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I77" t="str">
-        <v>Bar Standard</v>
-      </c>
-      <c r="J77" t="str">
-        <v>(blank)</v>
+        <v>Maquis</v>
+      </c>
+      <c r="J77">
+        <v>707321727</v>
       </c>
       <c r="K77">
-        <v>5.43858</v>
+        <v>5.4457</v>
       </c>
       <c r="L77">
-        <v>-4.01252</v>
+        <v>-4.02223</v>
       </c>
     </row>
     <row r="78">
@@ -3341,34 +3335,34 @@
         <v>46167</v>
       </c>
       <c r="C78" t="str">
-        <v>LANDRY TIEHI</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D78" t="str">
-        <v>ABVD.01.06</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E78" t="str">
-        <v>Chez Ivan</v>
+        <v>LE BRUNCH CHEZ M.J</v>
       </c>
       <c r="F78">
-        <v>10437433</v>
+        <v>10448467</v>
       </c>
       <c r="G78" t="str">
-        <v>DB010126N001777</v>
+        <v>DB010126N005913</v>
       </c>
       <c r="H78" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I78" t="str">
-        <v>Maquis Choco</v>
+        <v>Maquis</v>
       </c>
       <c r="J78" t="str">
-        <v>(blank)</v>
+        <v>07 07 99 74 49</v>
       </c>
       <c r="K78">
-        <v>5.4085</v>
+        <v>5.37373</v>
       </c>
       <c r="L78">
-        <v>-4.00558</v>
+        <v>-3.92237</v>
       </c>
     </row>
     <row r="79">
@@ -3379,34 +3373,34 @@
         <v>46167</v>
       </c>
       <c r="C79" t="str">
-        <v>MARC AMON</v>
+        <v>HERMANN GOGOUA</v>
       </c>
       <c r="D79" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.04.02</v>
       </c>
       <c r="E79" t="str">
-        <v>Le Massada</v>
+        <v>Fashion</v>
       </c>
       <c r="F79">
-        <v>10443627</v>
+        <v>10436626</v>
       </c>
       <c r="G79" t="str">
-        <v>DB010126N003341</v>
+        <v>DB010126N001383</v>
       </c>
       <c r="H79" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I79" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J79">
-        <v>1023456789</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J79" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K79">
-        <v>5.32257</v>
+        <v>5.34865</v>
       </c>
       <c r="L79">
-        <v>-4.07208</v>
+        <v>-3.94311</v>
       </c>
     </row>
     <row r="80">
@@ -3417,34 +3411,34 @@
         <v>46167</v>
       </c>
       <c r="C80" t="str">
-        <v>LANDRY TIEHI</v>
+        <v>RODRIGUE YOHORE</v>
       </c>
       <c r="D80" t="str">
-        <v>ABVD.01.06</v>
+        <v>ABVI.05.04</v>
       </c>
       <c r="E80" t="str">
-        <v>Cave des varons</v>
+        <v>Maquis au palmier</v>
       </c>
       <c r="F80">
-        <v>10437409</v>
+        <v>10449202</v>
       </c>
       <c r="G80" t="str">
-        <v>DB010126N007166</v>
+        <v>DB010126N017739</v>
       </c>
       <c r="H80" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I80" t="str">
-        <v>Maquis Choco</v>
-      </c>
-      <c r="J80" t="str">
-        <v>(blank)</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J80">
+        <v>142803414</v>
       </c>
       <c r="K80">
-        <v>5.40946</v>
+        <v>5.4439919</v>
       </c>
       <c r="L80">
-        <v>-4.00396</v>
+        <v>-3.9816895</v>
       </c>
     </row>
     <row r="81">
@@ -3455,34 +3449,34 @@
         <v>46167</v>
       </c>
       <c r="C81" t="str">
-        <v>FRANCK YAO</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D81" t="str">
-        <v>ABVI.03.02</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E81" t="str">
-        <v>MAQUIS CP1</v>
+        <v>Gagnoa gare</v>
       </c>
       <c r="F81">
-        <v>10450593</v>
+        <v>10443985</v>
       </c>
       <c r="G81" t="str">
-        <v>DB010126N019562</v>
+        <v>DB010126N003696</v>
       </c>
       <c r="H81" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I81" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J81">
-        <v>779522825</v>
+        <v>707600546</v>
       </c>
       <c r="K81">
-        <v>5.2431108</v>
+        <v>5.28359</v>
       </c>
       <c r="L81">
-        <v>-3.9159701</v>
+        <v>-3.96783</v>
       </c>
     </row>
     <row r="82">
@@ -3493,34 +3487,34 @@
         <v>46167</v>
       </c>
       <c r="C82" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>EULOGE ESSIS</v>
       </c>
       <c r="D82" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVD.01.04</v>
       </c>
       <c r="E82" t="str">
-        <v>VSD</v>
+        <v>Le bon vieux temps</v>
       </c>
       <c r="F82">
-        <v>10449551</v>
+        <v>10442767</v>
       </c>
       <c r="G82" t="str">
-        <v>DB010126N024730</v>
+        <v>DB010126N002487</v>
       </c>
       <c r="H82" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I82" t="str">
-        <v>Bar Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J82">
-        <v>706881775</v>
+        <v>788037883</v>
       </c>
       <c r="K82">
-        <v>5.3525148</v>
+        <v>5.368269</v>
       </c>
       <c r="L82">
-        <v>-3.9385876</v>
+        <v>-4.004642</v>
       </c>
     </row>
     <row r="83">
@@ -3531,34 +3525,34 @@
         <v>46167</v>
       </c>
       <c r="C83" t="str">
-        <v>MARC AMON</v>
+        <v>JOSEPH ABOUA</v>
       </c>
       <c r="D83" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.03.03</v>
       </c>
       <c r="E83" t="str">
-        <v xml:space="preserve">Cœur blanc sideci </v>
+        <v>La cave d’Anani</v>
       </c>
       <c r="F83">
-        <v>10448730</v>
+        <v>10448518</v>
       </c>
       <c r="G83" t="str">
-        <v>DB010126N006134</v>
+        <v>DB010126N005961</v>
       </c>
       <c r="H83" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I83" t="str">
-        <v>Bar</v>
-      </c>
-      <c r="J83" t="str">
-        <v>(blank)</v>
+        <v>Maquis</v>
+      </c>
+      <c r="J83">
+        <v>747878296</v>
       </c>
       <c r="K83">
-        <v>5.32232</v>
+        <v>5.23845</v>
       </c>
       <c r="L83">
-        <v>-4.08034</v>
+        <v>-3.87316</v>
       </c>
     </row>
     <row r="84">
@@ -3569,34 +3563,34 @@
         <v>46167</v>
       </c>
       <c r="C84" t="str">
-        <v>TCHESSE GOHOURE</v>
+        <v>Berenger-Orphée Jenifer Okou</v>
       </c>
       <c r="D84" t="str">
-        <v>ABVI.02.02</v>
+        <v>ABVI.02.H2</v>
       </c>
       <c r="E84" t="str">
-        <v>Au palais</v>
+        <v>La Station</v>
       </c>
       <c r="F84">
-        <v>10439362</v>
+        <v>10435877</v>
       </c>
       <c r="G84" t="str">
-        <v>DB010126N006998</v>
+        <v>DB010126N001167</v>
       </c>
       <c r="H84" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I84" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J84" t="str">
-        <v>(blank)</v>
+        <v>Bar</v>
+      </c>
+      <c r="J84">
+        <v>708398756</v>
       </c>
       <c r="K84">
-        <v>5.34316</v>
+        <v>5.30196</v>
       </c>
       <c r="L84">
-        <v>-3.96977</v>
+        <v>-4.00052</v>
       </c>
     </row>
     <row r="85">
@@ -3607,34 +3601,34 @@
         <v>46167</v>
       </c>
       <c r="C85" t="str">
-        <v>SAHI DIOMANDE</v>
+        <v>AMINE COULIBALY</v>
       </c>
       <c r="D85" t="str">
-        <v>ABVI.05.01</v>
+        <v>ABVD.01.01</v>
       </c>
       <c r="E85" t="str">
-        <v>Vip petit vélo</v>
+        <v>La cave du Repaire</v>
       </c>
       <c r="F85">
-        <v>10438381</v>
+        <v>10433108</v>
       </c>
       <c r="G85" t="str">
-        <v>DB010126N002066</v>
+        <v>DB010126N000113</v>
       </c>
       <c r="H85" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I85" t="str">
-        <v>Bar Standard</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J85" t="str">
         <v>(blank)</v>
       </c>
       <c r="K85">
-        <v>5.32252</v>
+        <v>5.36633</v>
       </c>
       <c r="L85">
-        <v>-4.03624</v>
+        <v>-4.02276</v>
       </c>
     </row>
     <row r="86">
@@ -3645,34 +3639,31 @@
         <v>46168</v>
       </c>
       <c r="C86" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>Innocent Yoboue</v>
       </c>
       <c r="D86" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVI.02.05</v>
       </c>
       <c r="E86" t="str">
-        <v>Chez Aicha</v>
+        <v>Cave</v>
       </c>
       <c r="F86">
-        <v>10449621</v>
+        <v>10434096</v>
       </c>
       <c r="G86" t="str">
-        <v>DB010126N009316</v>
+        <v>DB010126N008438</v>
       </c>
       <c r="H86" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I86" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J86">
-        <v>574947572</v>
+        <v>Maquis Choco</v>
       </c>
       <c r="K86">
-        <v>5.3621112</v>
+        <v>5.30955</v>
       </c>
       <c r="L86">
-        <v>-3.9364354</v>
+        <v>-3.95084</v>
       </c>
     </row>
     <row r="87">
@@ -3683,19 +3674,19 @@
         <v>46168</v>
       </c>
       <c r="C87" t="str">
-        <v>TCHESSE GOHOURE</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D87" t="str">
-        <v>ABVI.02.02</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E87" t="str">
-        <v>Chival s</v>
+        <v>Au palmier</v>
       </c>
       <c r="F87">
-        <v>10449695</v>
+        <v>10449932</v>
       </c>
       <c r="G87" t="str">
-        <v>DB010126N015832</v>
+        <v>DB010126N007516</v>
       </c>
       <c r="H87" t="str">
         <v>ABIDJAN</v>
@@ -3704,13 +3695,13 @@
         <v>Maquis Standard</v>
       </c>
       <c r="J87">
-        <v>709830490</v>
+        <v>707110931</v>
       </c>
       <c r="K87">
-        <v>5.3394371</v>
+        <v>5.2866458</v>
       </c>
       <c r="L87">
-        <v>-3.9743245</v>
+        <v>-3.9568494</v>
       </c>
     </row>
     <row r="88">
@@ -3721,34 +3712,34 @@
         <v>46168</v>
       </c>
       <c r="C88" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>MARC AMON</v>
       </c>
       <c r="D88" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVD.01.07</v>
       </c>
       <c r="E88" t="str">
-        <v>Boya clubs vip</v>
+        <v>Chine populaire</v>
       </c>
       <c r="F88">
-        <v>10446590</v>
+        <v>10444790</v>
       </c>
       <c r="G88" t="str">
-        <v>DB010126N005524</v>
+        <v>DB010126N003980</v>
       </c>
       <c r="H88" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I88" t="str">
-        <v>Bar</v>
+        <v>Maquis</v>
       </c>
       <c r="J88">
-        <v>778343833</v>
+        <v>705128078</v>
       </c>
       <c r="K88">
-        <v>5.32197</v>
+        <v>5.32345</v>
       </c>
       <c r="L88">
-        <v>-4.00263</v>
+        <v>-4.05906</v>
       </c>
     </row>
     <row r="89">
@@ -3759,34 +3750,34 @@
         <v>46168</v>
       </c>
       <c r="C89" t="str">
-        <v>ALEXANDRE TIEGBE</v>
+        <v>Berenger-Orphée Jenifer Okou</v>
       </c>
       <c r="D89" t="str">
-        <v>ABVI.01.02</v>
+        <v>ABVI.02.H2</v>
       </c>
       <c r="E89" t="str">
-        <v>JOCK VIp</v>
+        <v>Rose blanc</v>
       </c>
       <c r="F89">
-        <v>10432929</v>
+        <v>10435940</v>
       </c>
       <c r="G89" t="str">
-        <v>DB010126N000047</v>
+        <v>DB010126N001200</v>
       </c>
       <c r="H89" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I89" t="str">
-        <v>Bar Standard</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J89" t="str">
         <v>(blank)</v>
       </c>
       <c r="K89">
-        <v>5.43479</v>
+        <v>5.30319</v>
       </c>
       <c r="L89">
-        <v>-4.01269</v>
+        <v>-4.00424</v>
       </c>
     </row>
     <row r="90">
@@ -3797,34 +3788,34 @@
         <v>46168</v>
       </c>
       <c r="C90" t="str">
-        <v>VERCRUSSE AGAH</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D90" t="str">
-        <v>ABVI.05.02</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E90" t="str">
-        <v>7 ÉTOILES 2 AKON</v>
+        <v>Maquis ya Dieu dedans</v>
       </c>
       <c r="F90">
-        <v>10445339</v>
+        <v>10437354</v>
       </c>
       <c r="G90" t="str">
-        <v>DB010126N004385</v>
+        <v>DB010126N001755</v>
       </c>
       <c r="H90" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I90" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J90">
-        <v>555001188</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J90" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K90">
-        <v>5.52797</v>
+        <v>5.28031</v>
       </c>
       <c r="L90">
-        <v>-4.09404</v>
+        <v>-3.94777</v>
       </c>
     </row>
     <row r="91">
@@ -3835,34 +3826,34 @@
         <v>46168</v>
       </c>
       <c r="C91" t="str">
-        <v>AIME KONAN</v>
+        <v>LANDRY TIEHI</v>
       </c>
       <c r="D91" t="str">
-        <v>ABVI.04.04</v>
+        <v>ABVD.01.06</v>
       </c>
       <c r="E91" t="str">
-        <v>Conquistador</v>
+        <v>LA PISCINE</v>
       </c>
       <c r="F91">
-        <v>10439830</v>
+        <v>10443776</v>
       </c>
       <c r="G91" t="str">
-        <v>DB010126N007547</v>
+        <v>DB010126N003491</v>
       </c>
       <c r="H91" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I91" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J91" t="str">
-        <v>(blank)</v>
+        <v>Maquis</v>
+      </c>
+      <c r="J91">
+        <v>501210172</v>
       </c>
       <c r="K91">
-        <v>5.3976</v>
+        <v>5.40348</v>
       </c>
       <c r="L91">
-        <v>-3.94674</v>
+        <v>-3.9784</v>
       </c>
     </row>
     <row r="92">
@@ -3873,19 +3864,19 @@
         <v>46168</v>
       </c>
       <c r="C92" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>LAETITIA KISSI</v>
       </c>
       <c r="D92" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVD.02.05</v>
       </c>
       <c r="E92" t="str">
-        <v>Chez Aya</v>
+        <v>MAQUIS chez DIANE</v>
       </c>
       <c r="F92">
-        <v>10449623</v>
+        <v>10450314</v>
       </c>
       <c r="G92" t="str">
-        <v>DB010126N009493</v>
+        <v>DB010126N018374</v>
       </c>
       <c r="H92" t="str">
         <v>ABIDJAN</v>
@@ -3894,13 +3885,13 @@
         <v>Maquis Standard</v>
       </c>
       <c r="J92">
-        <v>150907259</v>
+        <v>707443749</v>
       </c>
       <c r="K92">
-        <v>5.3488262</v>
+        <v>5.3231667</v>
       </c>
       <c r="L92">
-        <v>-3.9408263</v>
+        <v>-4.093895</v>
       </c>
     </row>
     <row r="93">
@@ -3911,34 +3902,34 @@
         <v>46168</v>
       </c>
       <c r="C93" t="str">
-        <v>MARC AMON</v>
+        <v>Guy-Evrard Fodjo</v>
       </c>
       <c r="D93" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVD.02.04</v>
       </c>
       <c r="E93" t="str">
-        <v>Chine populaire</v>
+        <v>Le chatelet</v>
       </c>
       <c r="F93">
-        <v>10444790</v>
+        <v>10434826</v>
       </c>
       <c r="G93" t="str">
-        <v>DB010126N003980</v>
+        <v>DB010126N000761</v>
       </c>
       <c r="H93" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I93" t="str">
-        <v>Maquis</v>
-      </c>
-      <c r="J93">
-        <v>705128078</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J93" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K93">
-        <v>5.32345</v>
+        <v>5.43721</v>
       </c>
       <c r="L93">
-        <v>-4.05906</v>
+        <v>-4.03697</v>
       </c>
     </row>
     <row r="94">
@@ -3949,34 +3940,34 @@
         <v>46168</v>
       </c>
       <c r="C94" t="str">
-        <v>VERCRUSSE AGAH</v>
+        <v>Berenger-Orphée Jenifer Okou</v>
       </c>
       <c r="D94" t="str">
-        <v>ABVI.05.02</v>
+        <v>ABVI.02.H2</v>
       </c>
       <c r="E94" t="str">
-        <v>Hôtel resto Vegas</v>
+        <v>Sous l'accassia</v>
       </c>
       <c r="F94">
-        <v>10439645</v>
+        <v>10435945</v>
       </c>
       <c r="G94" t="str">
-        <v>DB010126N002377</v>
+        <v>DB010126N001202</v>
       </c>
       <c r="H94" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I94" t="str">
-        <v>HÔTEL LOCAL</v>
-      </c>
-      <c r="J94">
-        <v>707297919</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J94" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K94">
-        <v>5.4677133</v>
+        <v>5.30658</v>
       </c>
       <c r="L94">
-        <v>-4.0385167</v>
+        <v>-4.00309</v>
       </c>
     </row>
     <row r="95">
@@ -3987,19 +3978,19 @@
         <v>46168</v>
       </c>
       <c r="C95" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>AMINE COULIBALY</v>
       </c>
       <c r="D95" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVD.01.01</v>
       </c>
       <c r="E95" t="str">
-        <v>Maquis chez YAPI</v>
+        <v>ADEMELE BAR</v>
       </c>
       <c r="F95">
-        <v>10449615</v>
+        <v>10433031</v>
       </c>
       <c r="G95" t="str">
-        <v>DB010126N019404</v>
+        <v>DB010126N000077</v>
       </c>
       <c r="H95" t="str">
         <v>ABIDJAN</v>
@@ -4007,14 +3998,14 @@
       <c r="I95" t="str">
         <v>Maquis Standard</v>
       </c>
-      <c r="J95">
-        <v>779124211</v>
+      <c r="J95" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K95">
-        <v>5.3949853</v>
+        <v>5.36079</v>
       </c>
       <c r="L95">
-        <v>-3.9571197</v>
+        <v>-4.02562</v>
       </c>
     </row>
     <row r="96">
@@ -4025,19 +4016,19 @@
         <v>46168</v>
       </c>
       <c r="C96" t="str">
-        <v>Guy-Evrard Fodjo</v>
+        <v>MARC AMON</v>
       </c>
       <c r="D96" t="str">
-        <v>ABVD.02.04</v>
+        <v>ABVD.01.07</v>
       </c>
       <c r="E96" t="str">
-        <v>ZOUGLOU KAMIKASE</v>
+        <v>Maquis Chez floo</v>
       </c>
       <c r="F96">
-        <v>10434929</v>
+        <v>10437761</v>
       </c>
       <c r="G96" t="str">
-        <v>DB010126N000790</v>
+        <v>DB010126N001843</v>
       </c>
       <c r="H96" t="str">
         <v>ABIDJAN</v>
@@ -4049,10 +4040,10 @@
         <v>(blank)</v>
       </c>
       <c r="K96">
-        <v>5.43354</v>
+        <v>5.32185</v>
       </c>
       <c r="L96">
-        <v>-4.03704</v>
+        <v>-4.10529</v>
       </c>
     </row>
     <row r="97">
@@ -4063,19 +4054,19 @@
         <v>46168</v>
       </c>
       <c r="C97" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>HERMANN GOGOUA</v>
       </c>
       <c r="D97" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVI.04.02</v>
       </c>
       <c r="E97" t="str">
-        <v>MAISON BLANCHE</v>
+        <v>Au gbêssê</v>
       </c>
       <c r="F97">
-        <v>10450084</v>
+        <v>10436555</v>
       </c>
       <c r="G97" t="str">
-        <v>DB010126N006863</v>
+        <v>DB010126N001354</v>
       </c>
       <c r="H97" t="str">
         <v>ABIDJAN</v>
@@ -4087,10 +4078,10 @@
         <v>(blank)</v>
       </c>
       <c r="K97">
-        <v>5.30417</v>
+        <v>5.34001</v>
       </c>
       <c r="L97">
-        <v>-4.01366</v>
+        <v>-3.9446</v>
       </c>
     </row>
     <row r="98">
@@ -4101,19 +4092,19 @@
         <v>46169</v>
       </c>
       <c r="C98" t="str">
-        <v>MARC AMON</v>
+        <v>FRANCK YAO</v>
       </c>
       <c r="D98" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.03.02</v>
       </c>
       <c r="E98" t="str">
-        <v>Chez Daniel</v>
+        <v>La terre béni chez digbeu</v>
       </c>
       <c r="F98">
-        <v>10450376</v>
+        <v>10435398</v>
       </c>
       <c r="G98" t="str">
-        <v>DB010126N009740</v>
+        <v>DB010126N007827</v>
       </c>
       <c r="H98" t="str">
         <v>ABIDJAN</v>
@@ -4121,14 +4112,14 @@
       <c r="I98" t="str">
         <v>Maquis Standard</v>
       </c>
-      <c r="J98">
-        <v>546849776</v>
+      <c r="J98" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K98">
-        <v>5.32314</v>
+        <v>5.24862</v>
       </c>
       <c r="L98">
-        <v>-4.0710471</v>
+        <v>-3.95146</v>
       </c>
     </row>
     <row r="99">
@@ -4139,34 +4130,34 @@
         <v>46169</v>
       </c>
       <c r="C99" t="str">
-        <v>EPONOH ETTIEN</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D99" t="str">
-        <v>ABVI.05.H4</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E99" t="str">
-        <v>Cave SCYA</v>
+        <v>Maquis chez Gbazé</v>
       </c>
       <c r="F99">
-        <v>10434313</v>
+        <v>10439899</v>
       </c>
       <c r="G99" t="str">
-        <v>DB010126N000552</v>
+        <v>DB010126N002453</v>
       </c>
       <c r="H99" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I99" t="str">
-        <v>Cave - On</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J99" t="str">
         <v>(blank)</v>
       </c>
       <c r="K99">
-        <v>5.35099</v>
+        <v>5.3672</v>
       </c>
       <c r="L99">
-        <v>-4.09735</v>
+        <v>-3.92177</v>
       </c>
     </row>
     <row r="100">
@@ -4177,19 +4168,19 @@
         <v>46169</v>
       </c>
       <c r="C100" t="str">
-        <v>AIME KONAN</v>
+        <v>MARC AMON</v>
       </c>
       <c r="D100" t="str">
-        <v>ABVI.04.04</v>
+        <v>ABVD.01.07</v>
       </c>
       <c r="E100" t="str">
-        <v>LE RENOUVEAU CHEZ SANDRA</v>
+        <v>Le wangrine</v>
       </c>
       <c r="F100">
-        <v>10443735</v>
+        <v>10444218</v>
       </c>
       <c r="G100" t="str">
-        <v>DB010126N003452</v>
+        <v>DB010126N003930</v>
       </c>
       <c r="H100" t="str">
         <v>ABIDJAN</v>
@@ -4197,14 +4188,14 @@
       <c r="I100" t="str">
         <v>Maquis</v>
       </c>
-      <c r="J100" t="str">
-        <v>07 00 37 02 36</v>
+      <c r="J100">
+        <v>709896754</v>
       </c>
       <c r="K100">
-        <v>5.36336</v>
+        <v>5.32405</v>
       </c>
       <c r="L100">
-        <v>-3.89994</v>
+        <v>-4.07449</v>
       </c>
     </row>
     <row r="101">
@@ -4215,34 +4206,34 @@
         <v>46169</v>
       </c>
       <c r="C101" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>ALEXANDRE TIEGBE</v>
       </c>
       <c r="D101" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVI.01.02</v>
       </c>
       <c r="E101" t="str">
-        <v>Le Togo</v>
+        <v>Le bon coin</v>
       </c>
       <c r="F101">
-        <v>10435890</v>
+        <v>10450551</v>
       </c>
       <c r="G101" t="str">
-        <v>DB010126N001175</v>
+        <v>DB010126N015621</v>
       </c>
       <c r="H101" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I101" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J101" t="str">
-        <v>(blank)</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J101">
+        <v>707188063</v>
       </c>
       <c r="K101">
-        <v>5.30413</v>
+        <v>5.419031</v>
       </c>
       <c r="L101">
-        <v>-4.00583</v>
+        <v>-4.0065909</v>
       </c>
     </row>
     <row r="102">
@@ -4253,34 +4244,34 @@
         <v>46169</v>
       </c>
       <c r="C102" t="str">
-        <v>FRANCK YAO</v>
+        <v>EULOGE ESSIS</v>
       </c>
       <c r="D102" t="str">
-        <v>ABVI.03.02</v>
+        <v>ABVD.01.04</v>
       </c>
       <c r="E102" t="str">
-        <v>CAVE BELVA</v>
+        <v>Swell lounge</v>
       </c>
       <c r="F102">
-        <v>10435354</v>
+        <v>10449612</v>
       </c>
       <c r="G102" t="str">
-        <v>DB010126N007125</v>
+        <v>DB010126N023950</v>
       </c>
       <c r="H102" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I102" t="str">
-        <v>Cave - On</v>
-      </c>
-      <c r="J102" t="str">
-        <v>(blank)</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J102">
+        <v>708341143</v>
       </c>
       <c r="K102">
-        <v>5.24764</v>
+        <v>5.3617033</v>
       </c>
       <c r="L102">
-        <v>-3.9412</v>
+        <v>-3.9914952</v>
       </c>
     </row>
     <row r="103">
@@ -4291,34 +4282,34 @@
         <v>46169</v>
       </c>
       <c r="C103" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D103" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E103" t="str">
-        <v>Bleu blanc</v>
+        <v>MAQUIS RESTO LE PETIT VILLAGE</v>
       </c>
       <c r="F103">
-        <v>10449579</v>
+        <v>10449740</v>
       </c>
       <c r="G103" t="str">
-        <v>DB010126N008142</v>
+        <v>DB010126N021785</v>
       </c>
       <c r="H103" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I103" t="str">
-        <v>Maquis Choco</v>
+        <v>MAQUIS RESTAURANT</v>
       </c>
       <c r="J103">
-        <v>769886201</v>
+        <v>706076120</v>
       </c>
       <c r="K103">
-        <v>5.3231817</v>
+        <v>5.3497883</v>
       </c>
       <c r="L103">
-        <v>-3.9503483</v>
+        <v>-3.9736483</v>
       </c>
     </row>
     <row r="104">
@@ -4329,19 +4320,19 @@
         <v>46169</v>
       </c>
       <c r="C104" t="str">
-        <v>AMINE COULIBALY</v>
+        <v>ALEXANDRE TIEGBE</v>
       </c>
       <c r="D104" t="str">
-        <v>ABVD.01.01</v>
+        <v>ABVI.01.02</v>
       </c>
       <c r="E104" t="str">
-        <v>Cave chez Madame Ali</v>
+        <v>Chez Max Héro</v>
       </c>
       <c r="F104">
-        <v>10449296</v>
+        <v>10432894</v>
       </c>
       <c r="G104" t="str">
-        <v>DB010126N012207</v>
+        <v>DB010126N000034</v>
       </c>
       <c r="H104" t="str">
         <v>ABIDJAN</v>
@@ -4349,14 +4340,14 @@
       <c r="I104" t="str">
         <v>Maquis Standard</v>
       </c>
-      <c r="J104">
-        <v>504016026</v>
+      <c r="J104" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K104">
-        <v>5.3487244</v>
+        <v>5.41503</v>
       </c>
       <c r="L104">
-        <v>-4.0163927</v>
+        <v>-4.00155</v>
       </c>
     </row>
     <row r="105">
@@ -4367,34 +4358,34 @@
         <v>46169</v>
       </c>
       <c r="C105" t="str">
-        <v>Innocent Yoboue</v>
+        <v>FRANCK YAO</v>
       </c>
       <c r="D105" t="str">
-        <v>ABVI.02.05</v>
+        <v>ABVI.03.02</v>
       </c>
       <c r="E105" t="str">
-        <v>Chez Pascale</v>
+        <v>Belama</v>
       </c>
       <c r="F105">
-        <v>10445316</v>
+        <v>10450578</v>
       </c>
       <c r="G105" t="str">
-        <v>DB010126N004361</v>
+        <v>DB010126N011397</v>
       </c>
       <c r="H105" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I105" t="str">
-        <v>Maquis</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J105">
-        <v>596229248</v>
+        <v>747840756</v>
       </c>
       <c r="K105">
-        <v>5.31087</v>
+        <v>5.2555054</v>
       </c>
       <c r="L105">
-        <v>-3.94779</v>
+        <v>-3.9406055</v>
       </c>
     </row>
     <row r="106">
@@ -4405,34 +4396,34 @@
         <v>46169</v>
       </c>
       <c r="C106" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>LANDRY TIEHI</v>
       </c>
       <c r="D106" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVD.01.06</v>
       </c>
       <c r="E106" t="str">
-        <v>Cave la renaissance</v>
+        <v>La CACHETTE</v>
       </c>
       <c r="F106">
-        <v>10449620</v>
+        <v>10448382</v>
       </c>
       <c r="G106" t="str">
-        <v>DB010126N009051</v>
+        <v>DB010126N005875</v>
       </c>
       <c r="H106" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I106" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J106">
-        <v>767299255</v>
+        <v>789321725</v>
       </c>
       <c r="K106">
-        <v>5.3408409</v>
+        <v>5.42253</v>
       </c>
       <c r="L106">
-        <v>-4.0032263</v>
+        <v>-3.98126</v>
       </c>
     </row>
     <row r="107">
@@ -4443,34 +4434,34 @@
         <v>46169</v>
       </c>
       <c r="C107" t="str">
-        <v>EPONOH ETTIEN</v>
+        <v>TCHESSE GOHOURE</v>
       </c>
       <c r="D107" t="str">
-        <v>ABVI.05.H4</v>
+        <v>ABVI.02.02</v>
       </c>
       <c r="E107" t="str">
-        <v>chez Mimi</v>
+        <v>Z House</v>
       </c>
       <c r="F107">
-        <v>10450263</v>
+        <v>10434713</v>
       </c>
       <c r="G107" t="str">
-        <v>DB010126N011187</v>
+        <v>DB010126N008775</v>
       </c>
       <c r="H107" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I107" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J107">
-        <v>787083093</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J107" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K107">
-        <v>5.3526559</v>
+        <v>5.37009</v>
       </c>
       <c r="L107">
-        <v>-4.0965697</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="108">
@@ -4481,19 +4472,19 @@
         <v>46169</v>
       </c>
       <c r="C108" t="str">
-        <v>MARC AMON</v>
+        <v>VERCRUSSE AGAH</v>
       </c>
       <c r="D108" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVI.05.02</v>
       </c>
       <c r="E108" t="str">
-        <v>Cavé des rois</v>
+        <v>BIC BLEU</v>
       </c>
       <c r="F108">
-        <v>10444197</v>
+        <v>10445033</v>
       </c>
       <c r="G108" t="str">
-        <v>DB010126N003909</v>
+        <v>DB010126N004217</v>
       </c>
       <c r="H108" t="str">
         <v>ABIDJAN</v>
@@ -4502,13 +4493,13 @@
         <v>Maquis</v>
       </c>
       <c r="J108">
-        <v>142092453</v>
+        <v>749347362</v>
       </c>
       <c r="K108">
-        <v>5.32456</v>
+        <v>5.49689</v>
       </c>
       <c r="L108">
-        <v>-4.07947</v>
+        <v>-4.06007</v>
       </c>
     </row>
     <row r="109">
@@ -4519,34 +4510,34 @@
         <v>46169</v>
       </c>
       <c r="C109" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>ANGELIQUE KOUASSI</v>
       </c>
       <c r="D109" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVD.02.07</v>
       </c>
       <c r="E109" t="str">
-        <v>Pain condiments</v>
+        <v>2piments</v>
       </c>
       <c r="F109">
-        <v>10448341</v>
+        <v>10450195</v>
       </c>
       <c r="G109" t="str">
-        <v>DB010126N005856</v>
+        <v>DB010126N010494</v>
       </c>
       <c r="H109" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I109" t="str">
-        <v>Maquis</v>
+        <v>Maquis Standard</v>
       </c>
       <c r="J109">
-        <v>700767607</v>
+        <v>102026463</v>
       </c>
       <c r="K109">
-        <v>5.30449</v>
+        <v>5.3442461</v>
       </c>
       <c r="L109">
-        <v>-4.01308</v>
+        <v>-4.0665047</v>
       </c>
     </row>
     <row r="110">
@@ -4557,19 +4548,19 @@
         <v>46170</v>
       </c>
       <c r="C110" t="str">
-        <v>LANDRY TIEHI</v>
+        <v>AIME KONAN</v>
       </c>
       <c r="D110" t="str">
-        <v>ABVD.01.06</v>
+        <v>ABVI.04.04</v>
       </c>
       <c r="E110" t="str">
-        <v>CHEZ JULIE</v>
+        <v>MA CAVE</v>
       </c>
       <c r="F110">
-        <v>10448572</v>
+        <v>10443738</v>
       </c>
       <c r="G110" t="str">
-        <v>DB010126N006015</v>
+        <v>DB010126N003455</v>
       </c>
       <c r="H110" t="str">
         <v>ABIDJAN</v>
@@ -4577,14 +4568,14 @@
       <c r="I110" t="str">
         <v>Maquis</v>
       </c>
-      <c r="J110">
-        <v>747368911</v>
+      <c r="J110" t="str">
+        <v>07 09 09 10 46</v>
       </c>
       <c r="K110">
-        <v>5.3995</v>
+        <v>5.35513</v>
       </c>
       <c r="L110">
-        <v>-3.99624</v>
+        <v>-3.89434</v>
       </c>
     </row>
     <row r="111">
@@ -4601,28 +4592,28 @@
         <v>ABVI.01.02</v>
       </c>
       <c r="E111" t="str">
-        <v>Maquis La Gozor</v>
+        <v>WHATSAPP</v>
       </c>
       <c r="F111">
-        <v>10449237</v>
+        <v>10443643</v>
       </c>
       <c r="G111" t="str">
-        <v>DB010126N006484</v>
+        <v>DB010126N003357</v>
       </c>
       <c r="H111" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I111" t="str">
-        <v>MAQUIS RESTAURANT</v>
+        <v>Restaurant</v>
       </c>
       <c r="J111">
-        <v>554942275</v>
+        <v>584636883</v>
       </c>
       <c r="K111">
-        <v>5.412749</v>
+        <v>5.41264</v>
       </c>
       <c r="L111">
-        <v>-3.9964829</v>
+        <v>-3.99646</v>
       </c>
     </row>
     <row r="112">
@@ -4633,34 +4624,34 @@
         <v>46170</v>
       </c>
       <c r="C112" t="str">
-        <v>TCHESSE GOHOURE</v>
+        <v>FRANCK KOUADIO</v>
       </c>
       <c r="D112" t="str">
-        <v>ABVI.02.02</v>
+        <v>ABVD.02.03</v>
       </c>
       <c r="E112" t="str">
-        <v>Maquis resto chez maman Sabine</v>
+        <v>Chez fatou</v>
       </c>
       <c r="F112">
-        <v>10439517</v>
+        <v>10450018</v>
       </c>
       <c r="G112" t="str">
-        <v>DB010126N002341</v>
+        <v>DB010126N014041</v>
       </c>
       <c r="H112" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I112" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J112" t="str">
-        <v>(blank)</v>
+        <v>Cave</v>
+      </c>
+      <c r="J112">
+        <v>565254878</v>
       </c>
       <c r="K112">
-        <v>5.34932</v>
+        <v>5.319757</v>
       </c>
       <c r="L112">
-        <v>-3.96854</v>
+        <v>-4.2148078</v>
       </c>
     </row>
     <row r="113">
@@ -4671,34 +4662,34 @@
         <v>46170</v>
       </c>
       <c r="C113" t="str">
-        <v>LAFALI KONE</v>
+        <v>JOSEPH ABOUA</v>
       </c>
       <c r="D113" t="str">
-        <v>ABVI.02.03</v>
+        <v>ABVI.03.03</v>
       </c>
       <c r="E113" t="str">
-        <v>Restaurant OBV</v>
+        <v>Damas 2</v>
       </c>
       <c r="F113">
-        <v>10450016</v>
+        <v>10444056</v>
       </c>
       <c r="G113" t="str">
-        <v>DB010126N023507</v>
+        <v>DB010126N003768</v>
       </c>
       <c r="H113" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I113" t="str">
-        <v>Restaurant Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J113">
-        <v>757353378</v>
+        <v>789880725</v>
       </c>
       <c r="K113">
-        <v>5.2588958</v>
+        <v>5.24421</v>
       </c>
       <c r="L113">
-        <v>-3.9659516</v>
+        <v>-3.90198</v>
       </c>
     </row>
     <row r="114">
@@ -4709,34 +4700,34 @@
         <v>46170</v>
       </c>
       <c r="C114" t="str">
-        <v>HERMANN GOGOUA</v>
+        <v>VERCRUSSE AGAH</v>
       </c>
       <c r="D114" t="str">
-        <v>ABVI.04.02</v>
+        <v>ABVI.05.02</v>
       </c>
       <c r="E114" t="str">
-        <v>Chez Rosalie</v>
+        <v>Le wifi</v>
       </c>
       <c r="F114">
-        <v>10449633</v>
+        <v>10439689</v>
       </c>
       <c r="G114" t="str">
-        <v>DB010126N012400</v>
+        <v>DB010126N002387</v>
       </c>
       <c r="H114" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I114" t="str">
-        <v>Maquis Standard</v>
-      </c>
-      <c r="J114">
-        <v>758555931</v>
+        <v>Maquis Choco</v>
+      </c>
+      <c r="J114" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K114">
-        <v>5.3243783</v>
+        <v>5.46403</v>
       </c>
       <c r="L114">
-        <v>-4.0011367</v>
+        <v>-4.07663</v>
       </c>
     </row>
     <row r="115">
@@ -4747,19 +4738,19 @@
         <v>46170</v>
       </c>
       <c r="C115" t="str">
-        <v>Guy-Evrard Fodjo</v>
+        <v>LANDRY TIEHI</v>
       </c>
       <c r="D115" t="str">
-        <v>ABVD.02.04</v>
+        <v>ABVD.01.06</v>
       </c>
       <c r="E115" t="str">
-        <v>MAQUIS UNION</v>
+        <v>Agbovile continue</v>
       </c>
       <c r="F115">
-        <v>10434898</v>
+        <v>10437388</v>
       </c>
       <c r="G115" t="str">
-        <v>DB010126N000783</v>
+        <v>DB010126N001768</v>
       </c>
       <c r="H115" t="str">
         <v>ABIDJAN</v>
@@ -4771,10 +4762,10 @@
         <v>(blank)</v>
       </c>
       <c r="K115">
-        <v>5.44367</v>
+        <v>5.39565</v>
       </c>
       <c r="L115">
-        <v>-4.03005</v>
+        <v>-3.9997</v>
       </c>
     </row>
     <row r="116">
@@ -4785,19 +4776,19 @@
         <v>46170</v>
       </c>
       <c r="C116" t="str">
-        <v>Guy-Evrard Fodjo</v>
+        <v>HERMANN GOGOUA</v>
       </c>
       <c r="D116" t="str">
-        <v>ABVD.02.04</v>
+        <v>ABVI.04.02</v>
       </c>
       <c r="E116" t="str">
-        <v>Le palais de BC</v>
+        <v>Espace DIEU donné</v>
       </c>
       <c r="F116">
-        <v>10450458</v>
+        <v>10449722</v>
       </c>
       <c r="G116" t="str">
-        <v>DB010126N018253</v>
+        <v>DB010126N016392</v>
       </c>
       <c r="H116" t="str">
         <v>ABIDJAN</v>
@@ -4806,13 +4797,13 @@
         <v>MAQUIS RESTAURANT</v>
       </c>
       <c r="J116">
-        <v>747768786</v>
+        <v>170343297</v>
       </c>
       <c r="K116">
-        <v>5.4462566</v>
+        <v>5.3380971</v>
       </c>
       <c r="L116">
-        <v>-4.0207149</v>
+        <v>-3.9997469</v>
       </c>
     </row>
     <row r="117">
@@ -4823,34 +4814,34 @@
         <v>46170</v>
       </c>
       <c r="C117" t="str">
-        <v>ALEXANDRE TIEGBE</v>
+        <v>VERCRUSSE AGAH</v>
       </c>
       <c r="D117" t="str">
-        <v>ABVI.01.02</v>
+        <v>ABVI.05.02</v>
       </c>
       <c r="E117" t="str">
-        <v>Palais de la culture 2</v>
+        <v>Sans nom</v>
       </c>
       <c r="F117">
-        <v>10443638</v>
+        <v>10449094</v>
       </c>
       <c r="G117" t="str">
-        <v>DB010126N003352</v>
+        <v>DB010126N024491</v>
       </c>
       <c r="H117" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I117" t="str">
-        <v>Restaurant</v>
+        <v>Cave</v>
       </c>
       <c r="J117">
-        <v>779801709</v>
+        <v>747794604</v>
       </c>
       <c r="K117">
-        <v>5.41235</v>
+        <v>5.4506986</v>
       </c>
       <c r="L117">
-        <v>-3.99648</v>
+        <v>-4.059059</v>
       </c>
     </row>
     <row r="118">
@@ -4861,34 +4852,34 @@
         <v>46170</v>
       </c>
       <c r="C118" t="str">
-        <v>EULOGE ESSIS</v>
+        <v>LAFALI KONE</v>
       </c>
       <c r="D118" t="str">
-        <v>ABVD.01.04</v>
+        <v>ABVI.02.03</v>
       </c>
       <c r="E118" t="str">
-        <v>Pas de nom</v>
+        <v>Maquis au stand baye</v>
       </c>
       <c r="F118">
-        <v>10449713</v>
+        <v>10437285</v>
       </c>
       <c r="G118" t="str">
-        <v>DB010126N023860</v>
+        <v>DB010126N001717</v>
       </c>
       <c r="H118" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I118" t="str">
-        <v>MAQUIS RESTAURANT</v>
-      </c>
-      <c r="J118">
-        <v>709410264</v>
+        <v>Maquis Standard</v>
+      </c>
+      <c r="J118" t="str">
+        <v>(blank)</v>
       </c>
       <c r="K118">
-        <v>5.3674767</v>
+        <v>5.25891</v>
       </c>
       <c r="L118">
-        <v>-4.009841</v>
+        <v>-3.98108</v>
       </c>
     </row>
     <row r="119">
@@ -4899,34 +4890,34 @@
         <v>46170</v>
       </c>
       <c r="C119" t="str">
-        <v>Berenger-Orphée Jenifer Okou</v>
+        <v>MARC AMON</v>
       </c>
       <c r="D119" t="str">
-        <v>ABVI.02.H2</v>
+        <v>ABVD.01.07</v>
       </c>
       <c r="E119" t="str">
-        <v>Sweet cave</v>
+        <v>Maquis le secteur</v>
       </c>
       <c r="F119">
-        <v>10435949</v>
+        <v>10444219</v>
       </c>
       <c r="G119" t="str">
-        <v>DB010126N001203</v>
+        <v>DB010126N003931</v>
       </c>
       <c r="H119" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I119" t="str">
-        <v>Cave - On</v>
-      </c>
-      <c r="J119" t="str">
-        <v>(blank)</v>
+        <v>Maquis</v>
+      </c>
+      <c r="J119">
+        <v>779678954</v>
       </c>
       <c r="K119">
-        <v>5.30561</v>
+        <v>5.3249</v>
       </c>
       <c r="L119">
-        <v>-4.01288</v>
+        <v>-4.07839</v>
       </c>
     </row>
     <row r="120">
@@ -4937,34 +4928,34 @@
         <v>46170</v>
       </c>
       <c r="C120" t="str">
-        <v>MARC AMON</v>
+        <v>LANDRY TIEHI</v>
       </c>
       <c r="D120" t="str">
-        <v>ABVD.01.07</v>
+        <v>ABVD.01.06</v>
       </c>
       <c r="E120" t="str">
-        <v>Le temple</v>
+        <v>CHEZ JULIE</v>
       </c>
       <c r="F120">
-        <v>10450379</v>
+        <v>10448572</v>
       </c>
       <c r="G120" t="str">
-        <v>DB010126N018452</v>
+        <v>DB010126N006015</v>
       </c>
       <c r="H120" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I120" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J120">
-        <v>788798773</v>
+        <v>747368911</v>
       </c>
       <c r="K120">
-        <v>5.3249183</v>
+        <v>5.3995</v>
       </c>
       <c r="L120">
-        <v>-4.0765417</v>
+        <v>-3.99624</v>
       </c>
     </row>
     <row r="121">
@@ -4975,34 +4966,34 @@
         <v>46170</v>
       </c>
       <c r="C121" t="str">
-        <v>VERCRUSSE AGAH</v>
+        <v>LANDRY TIEHI</v>
       </c>
       <c r="D121" t="str">
-        <v>ABVI.05.02</v>
+        <v>ABVD.01.06</v>
       </c>
       <c r="E121" t="str">
-        <v>Cave arc-en ciel</v>
+        <v>Chez olivier</v>
       </c>
       <c r="F121">
-        <v>10449369</v>
+        <v>10443775</v>
       </c>
       <c r="G121" t="str">
-        <v>DB010126N011952</v>
+        <v>DB010126N003490</v>
       </c>
       <c r="H121" t="str">
         <v>ABIDJAN</v>
       </c>
       <c r="I121" t="str">
-        <v>Maquis Standard</v>
+        <v>Maquis</v>
       </c>
       <c r="J121">
-        <v>768442457</v>
+        <v>779725256</v>
       </c>
       <c r="K121">
-        <v>5.459072</v>
+        <v>5.40149</v>
       </c>
       <c r="L121">
-        <v>-4.069149</v>
+        <v>-4.00101</v>
       </c>
     </row>
   </sheetData>
